--- a/model performance comparison/Ratio_Cfree_Cnominal/Valdiviezo_data/Fischer model.xlsx
+++ b/model performance comparison/Ratio_Cfree_Cnominal/Valdiviezo_data/Fischer model.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Validation_alan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Paper writing\R1\model comparison_update_based reviewer\Validation_alan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E31C84-9A99-4BCD-ADD0-FB2AF8358CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7244E51A-C804-4DB5-B47C-D5D1E58F2C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model structure" sheetId="1" r:id="rId1"/>
     <sheet name="User input and model output" sheetId="4" r:id="rId2"/>
+    <sheet name="工作表1" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1952,6 +1953,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1987,143 +1992,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2212,6 +2080,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2239,8 +2113,135 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -3129,9 +3130,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3169,9 +3170,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3204,26 +3205,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3256,26 +3240,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3499,33 +3466,33 @@
     </row>
     <row r="2" spans="1:32" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A2" s="7"/>
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="104"/>
       <c r="I2" s="7"/>
-      <c r="J2" s="92" t="s">
+      <c r="J2" s="93" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="95"/>
       <c r="P2" s="7"/>
-      <c r="Q2" s="92" t="s">
+      <c r="Q2" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="R2" s="93"/>
-      <c r="S2" s="93"/>
-      <c r="T2" s="93"/>
-      <c r="U2" s="93"/>
-      <c r="V2" s="94"/>
+      <c r="R2" s="94"/>
+      <c r="S2" s="94"/>
+      <c r="T2" s="94"/>
+      <c r="U2" s="94"/>
+      <c r="V2" s="95"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
@@ -3551,19 +3518,19 @@
       <c r="G3" s="26"/>
       <c r="H3" s="27"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="97"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="98"/>
       <c r="P3" s="7"/>
-      <c r="Q3" s="95"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="96"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="97"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="98"/>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
@@ -3587,19 +3554,19 @@
       <c r="G4" s="29"/>
       <c r="H4" s="31"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="100"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="101"/>
       <c r="P4" s="7"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="99"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="99"/>
-      <c r="U4" s="99"/>
-      <c r="V4" s="100"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="101"/>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
@@ -14075,8 +14042,8 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -14109,19 +14076,19 @@
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="142" t="s">
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
-      <c r="L2" s="143"/>
-      <c r="M2" s="143"/>
-      <c r="N2" s="143"/>
-      <c r="O2" s="143"/>
-      <c r="P2" s="143"/>
-      <c r="Q2" s="144"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="107"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
@@ -14145,17 +14112,17 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="146"/>
-      <c r="K3" s="146"/>
-      <c r="L3" s="146"/>
-      <c r="M3" s="146"/>
-      <c r="N3" s="146"/>
-      <c r="O3" s="146"/>
-      <c r="P3" s="146"/>
-      <c r="Q3" s="147"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="109"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="109"/>
+      <c r="P3" s="109"/>
+      <c r="Q3" s="110"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -14179,17 +14146,17 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="149"/>
-      <c r="K4" s="149"/>
-      <c r="L4" s="149"/>
-      <c r="M4" s="149"/>
-      <c r="N4" s="149"/>
-      <c r="O4" s="149"/>
-      <c r="P4" s="149"/>
-      <c r="Q4" s="150"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="113"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -14213,19 +14180,19 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="129"/>
-      <c r="I5" s="151" t="s">
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="152"/>
-      <c r="K5" s="152"/>
-      <c r="L5" s="152"/>
-      <c r="M5" s="152"/>
-      <c r="N5" s="152"/>
-      <c r="O5" s="152"/>
-      <c r="P5" s="152"/>
-      <c r="Q5" s="153"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
+      <c r="N5" s="115"/>
+      <c r="O5" s="115"/>
+      <c r="P5" s="115"/>
+      <c r="Q5" s="116"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -14249,8 +14216,8 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="129"/>
-      <c r="H6" s="129"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
       <c r="I6" s="50" t="s">
         <v>51</v>
       </c>
@@ -14260,14 +14227,14 @@
       <c r="K6" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L6" s="121" t="s">
+      <c r="L6" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="122"/>
-      <c r="P6" s="122"/>
-      <c r="Q6" s="123"/>
+      <c r="M6" s="158"/>
+      <c r="N6" s="158"/>
+      <c r="O6" s="158"/>
+      <c r="P6" s="158"/>
+      <c r="Q6" s="159"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -14291,8 +14258,8 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
       <c r="I7" s="51" t="s">
         <v>21</v>
       </c>
@@ -14304,14 +14271,14 @@
         <f>J7/J7</f>
         <v>1</v>
       </c>
-      <c r="L7" s="104" t="s">
+      <c r="L7" s="151" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="105"/>
-      <c r="N7" s="105"/>
-      <c r="O7" s="105"/>
-      <c r="P7" s="105"/>
-      <c r="Q7" s="106"/>
+      <c r="M7" s="152"/>
+      <c r="N7" s="152"/>
+      <c r="O7" s="152"/>
+      <c r="P7" s="152"/>
+      <c r="Q7" s="153"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -14330,15 +14297,15 @@
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
-      <c r="B8" s="167" t="s">
+      <c r="B8" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="168"/>
-      <c r="D8" s="168"/>
-      <c r="E8" s="168"/>
-      <c r="F8" s="169"/>
-      <c r="G8" s="129"/>
-      <c r="H8" s="129"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="160"/>
       <c r="I8" s="52" t="s">
         <v>6</v>
       </c>
@@ -14350,14 +14317,14 @@
         <f>J8/J7</f>
         <v>0.99527166666666667</v>
       </c>
-      <c r="L8" s="104" t="s">
+      <c r="L8" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="105"/>
-      <c r="N8" s="105"/>
-      <c r="O8" s="105"/>
-      <c r="P8" s="105"/>
-      <c r="Q8" s="106"/>
+      <c r="M8" s="152"/>
+      <c r="N8" s="152"/>
+      <c r="O8" s="152"/>
+      <c r="P8" s="152"/>
+      <c r="Q8" s="153"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -14376,13 +14343,13 @@
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
-      <c r="B9" s="170"/>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="129"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
       <c r="I9" s="51" t="s">
         <v>8</v>
       </c>
@@ -14394,14 +14361,14 @@
         <f>J9/J7</f>
         <v>4.5739999999999999E-3</v>
       </c>
-      <c r="L9" s="104" t="s">
+      <c r="L9" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="105"/>
-      <c r="N9" s="105"/>
-      <c r="O9" s="105"/>
-      <c r="P9" s="105"/>
-      <c r="Q9" s="106"/>
+      <c r="M9" s="152"/>
+      <c r="N9" s="152"/>
+      <c r="O9" s="152"/>
+      <c r="P9" s="152"/>
+      <c r="Q9" s="153"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -14420,13 +14387,13 @@
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
-      <c r="B10" s="173"/>
-      <c r="C10" s="174"/>
-      <c r="D10" s="174"/>
-      <c r="E10" s="174"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="129"/>
+      <c r="B10" s="138"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
       <c r="I10" s="52" t="s">
         <v>9</v>
       </c>
@@ -14438,14 +14405,14 @@
         <f>J10/J7</f>
         <v>1.5433333333333331E-4</v>
       </c>
-      <c r="L10" s="104" t="s">
+      <c r="L10" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="M10" s="105"/>
-      <c r="N10" s="105"/>
-      <c r="O10" s="105"/>
-      <c r="P10" s="105"/>
-      <c r="Q10" s="106"/>
+      <c r="M10" s="152"/>
+      <c r="N10" s="152"/>
+      <c r="O10" s="152"/>
+      <c r="P10" s="152"/>
+      <c r="Q10" s="153"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -14464,24 +14431,24 @@
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
-      <c r="B11" s="132" t="s">
+      <c r="B11" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="134"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="120"/>
-      <c r="K11" s="120"/>
-      <c r="L11" s="120"/>
-      <c r="M11" s="120"/>
-      <c r="N11" s="120"/>
-      <c r="O11" s="120"/>
-      <c r="P11" s="120"/>
-      <c r="Q11" s="120"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="176"/>
+      <c r="M11" s="176"/>
+      <c r="N11" s="176"/>
+      <c r="O11" s="176"/>
+      <c r="P11" s="176"/>
+      <c r="Q11" s="176"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -14500,13 +14467,13 @@
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
-      <c r="B12" s="135"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
+      <c r="B12" s="144"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="146"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
       <c r="I12" s="50" t="s">
         <v>53</v>
       </c>
@@ -14516,14 +14483,14 @@
       <c r="K12" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="121" t="s">
+      <c r="L12" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="M12" s="122"/>
-      <c r="N12" s="122"/>
-      <c r="O12" s="122"/>
-      <c r="P12" s="122"/>
-      <c r="Q12" s="123"/>
+      <c r="M12" s="158"/>
+      <c r="N12" s="158"/>
+      <c r="O12" s="158"/>
+      <c r="P12" s="158"/>
+      <c r="Q12" s="159"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
@@ -14542,17 +14509,17 @@
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
-      <c r="B13" s="124" t="s">
+      <c r="B13" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="125"/>
-      <c r="D13" s="157" t="s">
+      <c r="C13" s="131"/>
+      <c r="D13" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="157"/>
-      <c r="F13" s="157"/>
-      <c r="G13" s="129"/>
-      <c r="H13" s="129"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
       <c r="I13" s="51" t="s">
         <v>5</v>
       </c>
@@ -14564,14 +14531,14 @@
         <f>J13/J13</f>
         <v>1</v>
       </c>
-      <c r="L13" s="104" t="s">
+      <c r="L13" s="151" t="s">
         <v>73</v>
       </c>
-      <c r="M13" s="105"/>
-      <c r="N13" s="105"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="105"/>
-      <c r="Q13" s="106"/>
+      <c r="M13" s="152"/>
+      <c r="N13" s="152"/>
+      <c r="O13" s="152"/>
+      <c r="P13" s="152"/>
+      <c r="Q13" s="153"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
@@ -14596,13 +14563,13 @@
       <c r="C14" s="44">
         <v>300</v>
       </c>
-      <c r="D14" s="158" t="s">
+      <c r="D14" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="158"/>
-      <c r="F14" s="158"/>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="160"/>
       <c r="I14" s="52" t="s">
         <v>45</v>
       </c>
@@ -14614,14 +14581,14 @@
         <f>J14/J13</f>
         <v>0.99527166666666667</v>
       </c>
-      <c r="L14" s="126" t="s">
+      <c r="L14" s="154" t="s">
         <v>72</v>
       </c>
-      <c r="M14" s="127"/>
-      <c r="N14" s="127"/>
-      <c r="O14" s="127"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="128"/>
+      <c r="M14" s="155"/>
+      <c r="N14" s="155"/>
+      <c r="O14" s="155"/>
+      <c r="P14" s="155"/>
+      <c r="Q14" s="156"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
@@ -14644,13 +14611,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="44"/>
-      <c r="D15" s="159" t="s">
+      <c r="D15" s="122" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="159"/>
-      <c r="F15" s="159"/>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="160"/>
       <c r="I15" s="51" t="s">
         <v>46</v>
       </c>
@@ -14662,14 +14629,14 @@
         <f>J15/J13</f>
         <v>4.5739999999999999E-3</v>
       </c>
-      <c r="L15" s="104" t="s">
+      <c r="L15" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="M15" s="105"/>
-      <c r="N15" s="105"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="105"/>
-      <c r="Q15" s="106"/>
+      <c r="M15" s="152"/>
+      <c r="N15" s="152"/>
+      <c r="O15" s="152"/>
+      <c r="P15" s="152"/>
+      <c r="Q15" s="153"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
@@ -14694,13 +14661,13 @@
       <c r="C16" s="45">
         <v>0.9</v>
       </c>
-      <c r="D16" s="160" t="s">
+      <c r="D16" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="161"/>
-      <c r="F16" s="162"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="160"/>
       <c r="I16" s="52" t="s">
         <v>47</v>
       </c>
@@ -14712,14 +14679,14 @@
         <f>J16/J13</f>
         <v>1.5433333333333331E-4</v>
       </c>
-      <c r="L16" s="104" t="s">
+      <c r="L16" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="M16" s="105"/>
-      <c r="N16" s="105"/>
-      <c r="O16" s="105"/>
-      <c r="P16" s="105"/>
-      <c r="Q16" s="106"/>
+      <c r="M16" s="152"/>
+      <c r="N16" s="152"/>
+      <c r="O16" s="152"/>
+      <c r="P16" s="152"/>
+      <c r="Q16" s="153"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
@@ -14744,22 +14711,22 @@
       <c r="C17" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="163" t="s">
+      <c r="D17" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="164"/>
-      <c r="F17" s="165"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="127"/>
-      <c r="L17" s="127"/>
-      <c r="M17" s="127"/>
-      <c r="N17" s="127"/>
-      <c r="O17" s="127"/>
-      <c r="P17" s="127"/>
-      <c r="Q17" s="128"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="160"/>
+      <c r="H17" s="160"/>
+      <c r="I17" s="154"/>
+      <c r="J17" s="155"/>
+      <c r="K17" s="155"/>
+      <c r="L17" s="155"/>
+      <c r="M17" s="155"/>
+      <c r="N17" s="155"/>
+      <c r="O17" s="155"/>
+      <c r="P17" s="155"/>
+      <c r="Q17" s="156"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -14784,13 +14751,13 @@
       <c r="C18" s="45">
         <v>0.1</v>
       </c>
-      <c r="D18" s="160" t="s">
+      <c r="D18" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="161"/>
-      <c r="F18" s="162"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="160"/>
       <c r="I18" s="50" t="s">
         <v>31</v>
       </c>
@@ -14800,14 +14767,14 @@
       <c r="K18" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L18" s="121" t="s">
+      <c r="L18" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="M18" s="122"/>
-      <c r="N18" s="122"/>
-      <c r="O18" s="122"/>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="123"/>
+      <c r="M18" s="158"/>
+      <c r="N18" s="158"/>
+      <c r="O18" s="158"/>
+      <c r="P18" s="158"/>
+      <c r="Q18" s="159"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -14826,13 +14793,13 @@
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
-      <c r="B19" s="159"/>
-      <c r="C19" s="159"/>
-      <c r="D19" s="159"/>
-      <c r="E19" s="159"/>
-      <c r="F19" s="159"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="160"/>
       <c r="I19" s="51" t="s">
         <v>5</v>
       </c>
@@ -14844,14 +14811,14 @@
         <f>J19/J19</f>
         <v>1</v>
       </c>
-      <c r="L19" s="104" t="s">
+      <c r="L19" s="151" t="s">
         <v>57</v>
       </c>
-      <c r="M19" s="105"/>
-      <c r="N19" s="105"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="105"/>
-      <c r="Q19" s="106"/>
+      <c r="M19" s="152"/>
+      <c r="N19" s="152"/>
+      <c r="O19" s="152"/>
+      <c r="P19" s="152"/>
+      <c r="Q19" s="153"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -14870,17 +14837,17 @@
     </row>
     <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
-      <c r="B20" s="124" t="s">
+      <c r="B20" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="125"/>
-      <c r="D20" s="157" t="s">
+      <c r="C20" s="131"/>
+      <c r="D20" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="157"/>
-      <c r="F20" s="157"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="129"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="160"/>
+      <c r="H20" s="160"/>
       <c r="I20" s="52" t="s">
         <v>45</v>
       </c>
@@ -14892,14 +14859,14 @@
         <f>J20/J19</f>
         <v>0.87354229684316542</v>
       </c>
-      <c r="L20" s="104" t="s">
+      <c r="L20" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="M20" s="105"/>
-      <c r="N20" s="105"/>
-      <c r="O20" s="105"/>
-      <c r="P20" s="105"/>
-      <c r="Q20" s="106"/>
+      <c r="M20" s="152"/>
+      <c r="N20" s="152"/>
+      <c r="O20" s="152"/>
+      <c r="P20" s="152"/>
+      <c r="Q20" s="153"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
@@ -14924,13 +14891,13 @@
       <c r="C21" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="163" t="s">
+      <c r="D21" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="164"/>
-      <c r="F21" s="165"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="129"/>
+      <c r="E21" s="127"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="160"/>
+      <c r="H21" s="160"/>
       <c r="I21" s="51" t="s">
         <v>46</v>
       </c>
@@ -14942,14 +14909,14 @@
         <f>J21/J19</f>
         <v>9.4560212233021856E-2</v>
       </c>
-      <c r="L21" s="104" t="s">
+      <c r="L21" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="M21" s="105"/>
-      <c r="N21" s="105"/>
-      <c r="O21" s="105"/>
-      <c r="P21" s="105"/>
-      <c r="Q21" s="106"/>
+      <c r="M21" s="152"/>
+      <c r="N21" s="152"/>
+      <c r="O21" s="152"/>
+      <c r="P21" s="152"/>
+      <c r="Q21" s="153"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -14974,13 +14941,13 @@
       <c r="C22" s="46">
         <v>1.0000000000000001E-30</v>
       </c>
-      <c r="D22" s="166" t="s">
+      <c r="D22" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="166"/>
-      <c r="F22" s="166"/>
-      <c r="G22" s="129"/>
-      <c r="H22" s="129"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="160"/>
+      <c r="H22" s="160"/>
       <c r="I22" s="53" t="s">
         <v>47</v>
       </c>
@@ -14992,14 +14959,14 @@
         <f>J22/J19</f>
         <v>3.1897490923812694E-2</v>
       </c>
-      <c r="L22" s="104" t="s">
+      <c r="L22" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="M22" s="105"/>
-      <c r="N22" s="105"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="105"/>
-      <c r="Q22" s="106"/>
+      <c r="M22" s="152"/>
+      <c r="N22" s="152"/>
+      <c r="O22" s="152"/>
+      <c r="P22" s="152"/>
+      <c r="Q22" s="153"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
@@ -15018,22 +14985,22 @@
     </row>
     <row r="23" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="7"/>
-      <c r="B23" s="154"/>
-      <c r="C23" s="155"/>
-      <c r="D23" s="155"/>
-      <c r="E23" s="155"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="116"/>
-      <c r="L23" s="116"/>
-      <c r="M23" s="116"/>
-      <c r="N23" s="116"/>
-      <c r="O23" s="116"/>
-      <c r="P23" s="116"/>
-      <c r="Q23" s="117"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="160"/>
+      <c r="H23" s="160"/>
+      <c r="I23" s="171"/>
+      <c r="J23" s="172"/>
+      <c r="K23" s="172"/>
+      <c r="L23" s="172"/>
+      <c r="M23" s="172"/>
+      <c r="N23" s="172"/>
+      <c r="O23" s="172"/>
+      <c r="P23" s="172"/>
+      <c r="Q23" s="173"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -15052,26 +15019,26 @@
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
-      <c r="B24" s="132" t="s">
+      <c r="B24" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="134"/>
-      <c r="G24" s="129"/>
-      <c r="H24" s="129"/>
-      <c r="I24" s="109" t="s">
+      <c r="C24" s="142"/>
+      <c r="D24" s="142"/>
+      <c r="E24" s="142"/>
+      <c r="F24" s="143"/>
+      <c r="G24" s="160"/>
+      <c r="H24" s="160"/>
+      <c r="I24" s="165" t="s">
         <v>44</v>
       </c>
-      <c r="J24" s="110"/>
-      <c r="K24" s="110"/>
-      <c r="L24" s="110"/>
-      <c r="M24" s="110"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="110"/>
-      <c r="P24" s="110"/>
-      <c r="Q24" s="111"/>
+      <c r="J24" s="166"/>
+      <c r="K24" s="166"/>
+      <c r="L24" s="166"/>
+      <c r="M24" s="166"/>
+      <c r="N24" s="166"/>
+      <c r="O24" s="166"/>
+      <c r="P24" s="166"/>
+      <c r="Q24" s="167"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
@@ -15090,22 +15057,22 @@
     </row>
     <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
-      <c r="B25" s="135"/>
-      <c r="C25" s="136"/>
-      <c r="D25" s="136"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="129"/>
-      <c r="H25" s="129"/>
-      <c r="I25" s="112"/>
-      <c r="J25" s="113"/>
-      <c r="K25" s="113"/>
-      <c r="L25" s="113"/>
-      <c r="M25" s="113"/>
-      <c r="N25" s="113"/>
-      <c r="O25" s="113"/>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="114"/>
+      <c r="B25" s="144"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="146"/>
+      <c r="G25" s="160"/>
+      <c r="H25" s="160"/>
+      <c r="I25" s="168"/>
+      <c r="J25" s="169"/>
+      <c r="K25" s="169"/>
+      <c r="L25" s="169"/>
+      <c r="M25" s="169"/>
+      <c r="N25" s="169"/>
+      <c r="O25" s="169"/>
+      <c r="P25" s="169"/>
+      <c r="Q25" s="170"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -15124,48 +15091,48 @@
     </row>
     <row r="26" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
-      <c r="B26" s="130" t="s">
+      <c r="B26" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="130" t="s">
+      <c r="C26" s="163" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="138" t="s">
+      <c r="D26" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="138" t="s">
+      <c r="E26" s="147" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="140" t="s">
+      <c r="F26" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="G26" s="129"/>
-      <c r="H26" s="129"/>
-      <c r="I26" s="118" t="s">
+      <c r="G26" s="160"/>
+      <c r="H26" s="160"/>
+      <c r="I26" s="174" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="118" t="s">
+      <c r="J26" s="174" t="s">
         <v>56</v>
       </c>
-      <c r="K26" s="107" t="s">
+      <c r="K26" s="161" t="s">
         <v>76</v>
       </c>
-      <c r="L26" s="107" t="s">
+      <c r="L26" s="161" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="107" t="s">
+      <c r="M26" s="161" t="s">
         <v>61</v>
       </c>
-      <c r="N26" s="107" t="s">
+      <c r="N26" s="161" t="s">
         <v>64</v>
       </c>
-      <c r="O26" s="107" t="s">
+      <c r="O26" s="161" t="s">
         <v>75</v>
       </c>
-      <c r="P26" s="107" t="s">
+      <c r="P26" s="161" t="s">
         <v>66</v>
       </c>
-      <c r="Q26" s="107" t="s">
+      <c r="Q26" s="161" t="s">
         <v>67</v>
       </c>
       <c r="R26" s="9"/>
@@ -15186,22 +15153,22 @@
     </row>
     <row r="27" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7"/>
-      <c r="B27" s="131"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="141"/>
-      <c r="G27" s="129"/>
-      <c r="H27" s="129"/>
-      <c r="I27" s="119"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="108"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="108"/>
-      <c r="N27" s="108"/>
-      <c r="O27" s="108"/>
-      <c r="P27" s="108"/>
-      <c r="Q27" s="108"/>
+      <c r="B27" s="164"/>
+      <c r="C27" s="164"/>
+      <c r="D27" s="148"/>
+      <c r="E27" s="148"/>
+      <c r="F27" s="150"/>
+      <c r="G27" s="160"/>
+      <c r="H27" s="160"/>
+      <c r="I27" s="175"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="162"/>
+      <c r="L27" s="162"/>
+      <c r="M27" s="162"/>
+      <c r="N27" s="162"/>
+      <c r="O27" s="162"/>
+      <c r="P27" s="162"/>
+      <c r="Q27" s="162"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
@@ -15227,31 +15194,31 @@
         <v>79</v>
       </c>
       <c r="D28" s="48">
-        <v>1.6437199999999998</v>
+        <v>-0.73745450190951667</v>
       </c>
       <c r="E28" s="48">
-        <v>1.9024449999999995</v>
+        <v>-1.5265197844064957</v>
       </c>
       <c r="F28" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G28" s="129"/>
-      <c r="H28" s="129"/>
+      <c r="G28" s="160"/>
+      <c r="H28" s="160"/>
       <c r="I28" s="55">
         <f t="shared" ref="I28:I47" si="1">IF(D28=0,"",LOG($K$15*10^D28+$K$16*10^E28+$K$14))</f>
-        <v>8.2419090837084263E-2</v>
+        <v>-1.6911818625904476E-3</v>
       </c>
       <c r="J28" s="55">
         <f t="shared" ref="J28:J47" si="2">IF(D28=0,"",LOG($K$21*10^D28+$K$22*10^E28+$K$20))</f>
-        <v>0.87994217322522461</v>
+        <v>-4.9732768954001666E-2</v>
       </c>
       <c r="K28" s="56">
         <f t="shared" ref="K28:K47" si="3">IF(D28=0,"",1/(1+10^D28*$J$15/$J$14+10^E28*$J$16/$J$14+10^J28*$J$19/$J$14))</f>
-        <v>0.82323258064396054</v>
+        <v>0.99915490018035669</v>
       </c>
       <c r="L28" s="56">
         <f t="shared" ref="L28:L47" si="4">IF(D28=0,"",1/(1+10^I28/10^J28*$J$13/$J$19))</f>
-        <v>6.3535126464640393E-38</v>
+        <v>9.0666996502323001E-39</v>
       </c>
       <c r="M28" s="56">
         <f t="shared" ref="M28:M47" si="5">IF(D28=0,"",1-L28)</f>
@@ -15259,21 +15226,24 @@
       </c>
       <c r="N28" s="56">
         <f t="shared" ref="N28:N47" si="6">IF(D28=0,"",1/(1/10^E28*$J$20/$J$22+10^D28/10^E28*$J$21/$J$22+10^I28/10^E28*$J$13/$J$22+1))</f>
-        <v>2.1343873978107244E-38</v>
+        <v>9.6475877256394232E-42</v>
       </c>
       <c r="O28" s="57">
         <f t="shared" ref="O28:O47" si="7">IF(D28=0,"",F28*K28*$J$7/$J$14)</f>
-        <v>8.2714359125795863E-7</v>
+        <v>1.0039016819665886E-6</v>
       </c>
       <c r="P28" s="57">
         <f t="shared" ref="P28:P47" si="8">IF(D28=0,"",O28*10^J28)</f>
-        <v>6.2736903923717607E-6</v>
+        <v>8.9527903147937384E-7</v>
       </c>
       <c r="Q28" s="57">
         <f t="shared" ref="Q28:Q47" si="9">IF(D28=0,"",F28*N28*$J$7/$J$22)</f>
-        <v>6.6073286486762687E-5</v>
-      </c>
-      <c r="R28" s="7"/>
+        <v>2.9865610542687298E-8</v>
+      </c>
+      <c r="R28" s="9">
+        <f>O28/F28</f>
+        <v>1.0039016819665887</v>
+      </c>
       <c r="S28" s="11"/>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -15306,8 +15276,8 @@
       <c r="F29" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G29" s="129"/>
-      <c r="H29" s="129"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="160"/>
       <c r="I29" s="55">
         <f t="shared" si="1"/>
         <v>2.552997157778905</v>
@@ -15344,7 +15314,10 @@
         <f t="shared" si="9"/>
         <v>1.9168354923060642E-3</v>
       </c>
-      <c r="R29" s="7"/>
+      <c r="R29" s="9">
+        <f t="shared" ref="R29:R47" si="10">O29/F29</f>
+        <v>2.7989996375041822E-3</v>
+      </c>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
@@ -15369,31 +15342,31 @@
         <v>83</v>
       </c>
       <c r="D30" s="90">
-        <v>7.1429999999999998</v>
+        <v>2.3724999877244022</v>
       </c>
       <c r="E30" s="90">
-        <v>9.299925</v>
+        <v>2.8974999825375303</v>
       </c>
       <c r="F30" s="91">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G30" s="129"/>
-      <c r="H30" s="129"/>
+      <c r="G30" s="160"/>
+      <c r="H30" s="160"/>
       <c r="I30" s="55">
         <f t="shared" si="1"/>
-        <v>5.5699117487608749</v>
+        <v>0.3415531664888502</v>
       </c>
       <c r="J30" s="55">
         <f t="shared" si="2"/>
-        <v>7.8125605305456389</v>
-      </c>
-      <c r="K30" s="176">
+        <v>1.6844884001093496</v>
+      </c>
+      <c r="K30" s="92">
         <f t="shared" si="3"/>
-        <v>2.6793527353994627E-6</v>
+        <v>0.45330287581188161</v>
       </c>
       <c r="L30" s="56">
         <f t="shared" si="4"/>
-        <v>1.7706780274273105E-36</v>
+        <v>2.230622353011702E-37</v>
       </c>
       <c r="M30" s="56">
         <f t="shared" si="5"/>
@@ -15401,21 +15374,24 @@
       </c>
       <c r="N30" s="56">
         <f t="shared" si="6"/>
-        <v>1.7348446458303191E-36</v>
+        <v>1.1619679650215839E-37</v>
       </c>
       <c r="O30" s="57">
         <f t="shared" si="7"/>
-        <v>2.6920817954891339E-12</v>
+        <v>4.5545642561097882E-7</v>
       </c>
       <c r="P30" s="57">
         <f t="shared" si="8"/>
-        <v>1.7484321424679768E-4</v>
+        <v>2.2025979649048948E-5</v>
       </c>
       <c r="Q30" s="57">
         <f t="shared" si="9"/>
-        <v>5.3704818259116245E-3</v>
-      </c>
-      <c r="R30" s="7"/>
+        <v>3.5970528274324124E-4</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="10"/>
+        <v>0.45545642561097882</v>
+      </c>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
@@ -15448,8 +15424,8 @@
       <c r="F31" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G31" s="129"/>
-      <c r="H31" s="129"/>
+      <c r="G31" s="160"/>
+      <c r="H31" s="160"/>
       <c r="I31" s="55">
         <f t="shared" si="1"/>
         <v>1.155792641235829</v>
@@ -15486,7 +15462,10 @@
         <f t="shared" si="9"/>
         <v>1.3817400909847816E-3</v>
       </c>
-      <c r="R31" s="7"/>
+      <c r="R31" s="9">
+        <f t="shared" si="10"/>
+        <v>6.9856586255860775E-2</v>
+      </c>
       <c r="S31" s="7"/>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
@@ -15519,8 +15498,8 @@
       <c r="F32" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G32" s="129"/>
-      <c r="H32" s="129"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="160"/>
       <c r="I32" s="55">
         <f t="shared" si="1"/>
         <v>3.7390634769430418</v>
@@ -15557,7 +15536,10 @@
         <f t="shared" si="9"/>
         <v>2.0002142780409164E-3</v>
       </c>
-      <c r="R32" s="7"/>
+      <c r="R32" s="9">
+        <f t="shared" si="10"/>
+        <v>1.8236291392664003E-4</v>
+      </c>
       <c r="S32" s="7"/>
       <c r="T32" s="7"/>
       <c r="U32" s="7"/>
@@ -15590,8 +15572,8 @@
       <c r="F33" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G33" s="129"/>
-      <c r="H33" s="129"/>
+      <c r="G33" s="160"/>
+      <c r="H33" s="160"/>
       <c r="I33" s="55">
         <f t="shared" si="1"/>
         <v>3.3165609217581955</v>
@@ -15628,7 +15610,10 @@
         <f t="shared" si="9"/>
         <v>1.636926118353416E-3</v>
       </c>
-      <c r="R33" s="7"/>
+      <c r="R33" s="9">
+        <f t="shared" si="10"/>
+        <v>4.8243530047943232E-4</v>
+      </c>
       <c r="S33" s="7"/>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
@@ -15661,8 +15646,8 @@
       <c r="F34" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G34" s="129"/>
-      <c r="H34" s="129"/>
+      <c r="G34" s="160"/>
+      <c r="H34" s="160"/>
       <c r="I34" s="55">
         <f t="shared" si="1"/>
         <v>3.2938799134674657</v>
@@ -15699,7 +15684,10 @@
         <f t="shared" si="9"/>
         <v>1.8793518098752537E-3</v>
       </c>
-      <c r="R34" s="7"/>
+      <c r="R34" s="9">
+        <f t="shared" si="10"/>
+        <v>5.0829997288154185E-4</v>
+      </c>
       <c r="S34" s="7"/>
       <c r="T34" s="7"/>
       <c r="U34" s="7"/>
@@ -15732,8 +15720,8 @@
       <c r="F35" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G35" s="129"/>
-      <c r="H35" s="129"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="160"/>
       <c r="I35" s="55">
         <f t="shared" si="1"/>
         <v>0.56442220215166938</v>
@@ -15770,7 +15758,10 @@
         <f t="shared" si="9"/>
         <v>4.8490403483442932E-4</v>
       </c>
-      <c r="R35" s="7"/>
+      <c r="R35" s="9">
+        <f t="shared" si="10"/>
+        <v>0.27263260787881261</v>
+      </c>
       <c r="S35" s="7"/>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
@@ -15795,31 +15786,31 @@
         <v>89</v>
       </c>
       <c r="D36" s="90">
-        <v>7.5547280000000008</v>
+        <v>3.9841999877244016</v>
       </c>
       <c r="E36" s="90">
-        <v>9.7459910000000001</v>
+        <v>5.1901999825375293</v>
       </c>
       <c r="F36" s="91">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G36" s="129"/>
-      <c r="H36" s="129"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="160"/>
       <c r="I36" s="55">
         <f t="shared" si="1"/>
-        <v>6.0102891918446346</v>
+        <v>1.8389468238593161</v>
       </c>
       <c r="J36" s="55">
         <f t="shared" si="2"/>
-        <v>8.2579578730069816</v>
-      </c>
-      <c r="K36" s="176">
+        <v>3.7675494433256032</v>
+      </c>
+      <c r="K36" s="92">
         <f t="shared" si="3"/>
-        <v>9.7196907873905555E-7</v>
+        <v>1.4420981407173024E-2</v>
       </c>
       <c r="L36" s="56">
         <f t="shared" si="4"/>
-        <v>1.7912635864903517E-36</v>
+        <v>8.5919835286250348E-37</v>
       </c>
       <c r="M36" s="56">
         <f t="shared" si="5"/>
@@ -15827,21 +15818,24 @@
       </c>
       <c r="N36" s="56">
         <f t="shared" si="6"/>
-        <v>1.7577177848516138E-36</v>
+        <v>7.2527130896336297E-37</v>
       </c>
       <c r="O36" s="57">
         <f t="shared" si="7"/>
-        <v>9.7658670621494186E-13</v>
+        <v>1.4489492557817235E-8</v>
       </c>
       <c r="P36" s="57">
         <f t="shared" si="8"/>
-        <v>1.7687590751903491E-4</v>
+        <v>8.4840382815560414E-5</v>
       </c>
       <c r="Q36" s="57">
         <f t="shared" si="9"/>
-        <v>5.4412891905426071E-3</v>
-      </c>
-      <c r="R36" s="7"/>
+        <v>2.2451903073883897E-3</v>
+      </c>
+      <c r="R36" s="9">
+        <f t="shared" si="10"/>
+        <v>1.4489492557817235E-2</v>
+      </c>
       <c r="S36" s="7"/>
       <c r="T36" s="7"/>
       <c r="U36" s="7"/>
@@ -15874,8 +15868,8 @@
       <c r="F37" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G37" s="129"/>
-      <c r="H37" s="129"/>
+      <c r="G37" s="160"/>
+      <c r="H37" s="160"/>
       <c r="I37" s="55">
         <f t="shared" si="1"/>
         <v>1.8993925761092847</v>
@@ -15912,7 +15906,10 @@
         <f t="shared" si="9"/>
         <v>1.6272430445916147E-3</v>
       </c>
-      <c r="R37" s="7"/>
+      <c r="R37" s="9">
+        <f t="shared" si="10"/>
+        <v>1.2606874337078583E-2</v>
+      </c>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
@@ -15945,8 +15942,8 @@
       <c r="F38" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G38" s="129"/>
-      <c r="H38" s="129"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="160"/>
       <c r="I38" s="55">
         <f t="shared" si="1"/>
         <v>0.66933218862556854</v>
@@ -15983,7 +15980,10 @@
         <f t="shared" si="9"/>
         <v>8.1258127703023549E-4</v>
       </c>
-      <c r="R38" s="7"/>
+      <c r="R38" s="9">
+        <f t="shared" si="10"/>
+        <v>0.2141252146705997</v>
+      </c>
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
@@ -16008,31 +16008,31 @@
         <v>94</v>
       </c>
       <c r="D39" s="48">
-        <v>-2.3039999999996397E-3</v>
+        <v>3.03</v>
       </c>
       <c r="E39" s="48">
-        <v>-1.314813</v>
+        <v>3.96</v>
       </c>
       <c r="F39" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G39" s="129"/>
-      <c r="H39" s="129"/>
+      <c r="G39" s="160"/>
+      <c r="H39" s="160"/>
       <c r="I39" s="55">
         <f t="shared" si="1"/>
-        <v>-7.429644403464382E-5</v>
+        <v>0.86355706001910959</v>
       </c>
       <c r="J39" s="55">
         <f t="shared" si="2"/>
-        <v>-1.3610239300554092E-2</v>
+        <v>2.5945087996693723</v>
       </c>
       <c r="K39" s="56">
         <f t="shared" si="3"/>
-        <v>0.99544194622158988</v>
+        <v>0.13626508164202661</v>
       </c>
       <c r="L39" s="56">
         <f t="shared" si="4"/>
-        <v>9.8164593715857243E-39</v>
+        <v>5.450577962533167E-37</v>
       </c>
       <c r="M39" s="56">
         <f t="shared" si="5"/>
@@ -16040,21 +16040,24 @@
       </c>
       <c r="N39" s="56">
         <f t="shared" si="6"/>
-        <v>1.5649794361852636E-41</v>
+        <v>4.0335763210518438E-37</v>
       </c>
       <c r="O39" s="57">
         <f t="shared" si="7"/>
-        <v>1.0001710885184681E-6</v>
+        <v>1.3691244933998919E-7</v>
       </c>
       <c r="P39" s="57">
         <f t="shared" si="8"/>
-        <v>9.6931304419295735E-7</v>
+        <v>5.3820997138407329E-5</v>
       </c>
       <c r="Q39" s="57">
         <f t="shared" si="9"/>
-        <v>4.8446376107272623E-8</v>
-      </c>
-      <c r="R39" s="7"/>
+        <v>1.2486563784083716E-3</v>
+      </c>
+      <c r="R39" s="9">
+        <f t="shared" si="10"/>
+        <v>0.1369124493399892</v>
+      </c>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
@@ -16087,8 +16090,8 @@
       <c r="F40" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G40" s="129"/>
-      <c r="H40" s="129"/>
+      <c r="G40" s="160"/>
+      <c r="H40" s="160"/>
       <c r="I40" s="55">
         <f t="shared" si="1"/>
         <v>0.98830104104276184</v>
@@ -16125,7 +16128,10 @@
         <f t="shared" si="9"/>
         <v>5.8369229297206666E-4</v>
       </c>
-      <c r="R40" s="7"/>
+      <c r="R40" s="9">
+        <f t="shared" si="10"/>
+        <v>0.1027303952296162</v>
+      </c>
       <c r="S40" s="7"/>
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
@@ -16158,8 +16164,8 @@
       <c r="F41" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G41" s="129"/>
-      <c r="H41" s="129"/>
+      <c r="G41" s="160"/>
+      <c r="H41" s="160"/>
       <c r="I41" s="55">
         <f t="shared" si="1"/>
         <v>1.0720640142200413</v>
@@ -16196,7 +16202,10 @@
         <f t="shared" si="9"/>
         <v>5.6163864871759586E-4</v>
       </c>
-      <c r="R41" s="7"/>
+      <c r="R41" s="9">
+        <f t="shared" si="10"/>
+        <v>8.471025435573197E-2</v>
+      </c>
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
@@ -16229,8 +16238,8 @@
       <c r="F42" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G42" s="129"/>
-      <c r="H42" s="129"/>
+      <c r="G42" s="160"/>
+      <c r="H42" s="160"/>
       <c r="I42" s="55">
         <f t="shared" si="1"/>
         <v>2.2754629671517499</v>
@@ -16267,7 +16276,10 @@
         <f t="shared" si="9"/>
         <v>2.3087400291566273E-3</v>
       </c>
-      <c r="R42" s="7"/>
+      <c r="R42" s="9">
+        <f t="shared" si="10"/>
+        <v>5.3031881166742028E-3</v>
+      </c>
       <c r="S42" s="7"/>
       <c r="T42" s="7"/>
       <c r="U42" s="7"/>
@@ -16300,8 +16312,8 @@
       <c r="F43" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G43" s="129"/>
-      <c r="H43" s="129"/>
+      <c r="G43" s="160"/>
+      <c r="H43" s="160"/>
       <c r="I43" s="55">
         <f t="shared" si="1"/>
         <v>2.0741209065073765</v>
@@ -16338,7 +16350,10 @@
         <f t="shared" si="9"/>
         <v>1.7153000232136746E-3</v>
       </c>
-      <c r="R43" s="7"/>
+      <c r="R43" s="9">
+        <f t="shared" si="10"/>
+        <v>8.4310000813626641E-3</v>
+      </c>
       <c r="S43" s="7"/>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
@@ -16371,8 +16386,8 @@
       <c r="F44" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G44" s="129"/>
-      <c r="H44" s="129"/>
+      <c r="G44" s="160"/>
+      <c r="H44" s="160"/>
       <c r="I44" s="55">
         <f t="shared" si="1"/>
         <v>0.62172127754097484</v>
@@ -16409,7 +16424,10 @@
         <f t="shared" si="9"/>
         <v>8.014246984332391E-4</v>
       </c>
-      <c r="R44" s="7"/>
+      <c r="R44" s="9">
+        <f t="shared" si="10"/>
+        <v>0.23893442294982087</v>
+      </c>
       <c r="S44" s="7"/>
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
@@ -16442,8 +16460,8 @@
       <c r="F45" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G45" s="129"/>
-      <c r="H45" s="129"/>
+      <c r="G45" s="160"/>
+      <c r="H45" s="160"/>
       <c r="I45" s="55">
         <f t="shared" si="1"/>
         <v>2.2151248995259314</v>
@@ -16480,7 +16498,10 @@
         <f t="shared" si="9"/>
         <v>1.1258670276074964E-3</v>
       </c>
-      <c r="R45" s="7"/>
+      <c r="R45" s="9">
+        <f t="shared" si="10"/>
+        <v>6.0936162463962286E-3</v>
+      </c>
       <c r="S45" s="7"/>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
@@ -16513,8 +16534,8 @@
       <c r="F46" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G46" s="129"/>
-      <c r="H46" s="129"/>
+      <c r="G46" s="160"/>
+      <c r="H46" s="160"/>
       <c r="I46" s="55">
         <f t="shared" si="1"/>
         <v>0.56702977498764862</v>
@@ -16551,7 +16572,10 @@
         <f t="shared" si="9"/>
         <v>7.3181654696612955E-4</v>
       </c>
-      <c r="R46" s="7"/>
+      <c r="R46" s="9">
+        <f t="shared" si="10"/>
+        <v>0.27100058290322826</v>
+      </c>
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
@@ -16584,8 +16608,8 @@
       <c r="F47" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="G47" s="129"/>
-      <c r="H47" s="129"/>
+      <c r="G47" s="160"/>
+      <c r="H47" s="160"/>
       <c r="I47" s="55">
         <f t="shared" si="1"/>
         <v>1.5670237821495228</v>
@@ -16622,7 +16646,10 @@
         <f t="shared" si="9"/>
         <v>4.9476186491981624E-4</v>
       </c>
-      <c r="R47" s="7"/>
+      <c r="R47" s="9">
+        <f t="shared" si="10"/>
+        <v>2.7100432247142064E-2</v>
+      </c>
       <c r="S47" s="7"/>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
@@ -16645,42 +16672,42 @@
       <c r="D48" s="84"/>
       <c r="E48" s="84"/>
       <c r="F48" s="85"/>
-      <c r="G48" s="129"/>
-      <c r="H48" s="129"/>
+      <c r="G48" s="160"/>
+      <c r="H48" s="160"/>
       <c r="I48" s="86" t="str">
-        <f t="shared" ref="I48:I50" si="10">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
+        <f t="shared" ref="I48:I50" si="11">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
         <v/>
       </c>
       <c r="J48" s="86" t="str">
-        <f t="shared" ref="J48:J50" si="11">IF(D48=0,"",LOG($K$21*10^D48+$K$22*10^E48+$K$20))</f>
+        <f t="shared" ref="J48:J50" si="12">IF(D48=0,"",LOG($K$21*10^D48+$K$22*10^E48+$K$20))</f>
         <v/>
       </c>
       <c r="K48" s="87" t="str">
-        <f t="shared" ref="K48:K50" si="12">IF(D48=0,"",1/(1+10^D48*$J$15/$J$14+10^E48*$J$16/$J$14+10^J48*$J$19/$J$14))</f>
+        <f t="shared" ref="K48:K50" si="13">IF(D48=0,"",1/(1+10^D48*$J$15/$J$14+10^E48*$J$16/$J$14+10^J48*$J$19/$J$14))</f>
         <v/>
       </c>
       <c r="L48" s="87" t="str">
-        <f t="shared" ref="L48:L50" si="13">IF(D48=0,"",1/(1+10^I48/10^J48*$J$13/$J$19))</f>
+        <f t="shared" ref="L48:L50" si="14">IF(D48=0,"",1/(1+10^I48/10^J48*$J$13/$J$19))</f>
         <v/>
       </c>
       <c r="M48" s="87" t="str">
-        <f t="shared" ref="M48:M92" si="14">IF(D48=0,"",1-L48)</f>
+        <f t="shared" ref="M48:M92" si="15">IF(D48=0,"",1-L48)</f>
         <v/>
       </c>
       <c r="N48" s="87" t="str">
-        <f t="shared" ref="N48:N50" si="15">IF(D48=0,"",1/(1/10^E48*$J$20/$J$22+10^D48/10^E48*$J$21/$J$22+10^I48/10^E48*$J$13/$J$22+1))</f>
+        <f t="shared" ref="N48:N50" si="16">IF(D48=0,"",1/(1/10^E48*$J$20/$J$22+10^D48/10^E48*$J$21/$J$22+10^I48/10^E48*$J$13/$J$22+1))</f>
         <v/>
       </c>
       <c r="O48" s="88" t="str">
-        <f t="shared" ref="O48:O92" si="16">IF(D48=0,"",F48*K48*$J$7/$J$14)</f>
+        <f t="shared" ref="O48:O92" si="17">IF(D48=0,"",F48*K48*$J$7/$J$14)</f>
         <v/>
       </c>
       <c r="P48" s="88" t="str">
-        <f t="shared" ref="P48:P50" si="17">IF(D48=0,"",O48*10^J48)</f>
+        <f t="shared" ref="P48:P50" si="18">IF(D48=0,"",O48*10^J48)</f>
         <v/>
       </c>
       <c r="Q48" s="88" t="str">
-        <f t="shared" ref="Q48:Q50" si="18">IF(D48=0,"",F48*N48*$J$7/$J$22)</f>
+        <f t="shared" ref="Q48:Q50" si="19">IF(D48=0,"",F48*N48*$J$7/$J$22)</f>
         <v/>
       </c>
       <c r="R48" s="7"/>
@@ -16708,53 +16735,56 @@
         <v>79</v>
       </c>
       <c r="D49" s="48">
-        <v>1.6437199999999998</v>
+        <v>-0.73745450190951667</v>
       </c>
       <c r="E49" s="48">
-        <v>1.9024449999999995</v>
+        <v>-1.5265197844064957</v>
       </c>
       <c r="F49" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G49" s="129"/>
-      <c r="H49" s="129"/>
+      <c r="G49" s="160"/>
+      <c r="H49" s="160"/>
       <c r="I49" s="55">
-        <f t="shared" si="10"/>
-        <v>8.2419090837084263E-2</v>
+        <f t="shared" si="11"/>
+        <v>-1.6911818625904476E-3</v>
       </c>
       <c r="J49" s="55">
-        <f t="shared" si="11"/>
-        <v>0.87994217322522461</v>
+        <f t="shared" si="12"/>
+        <v>-4.9732768954001666E-2</v>
       </c>
       <c r="K49" s="56">
-        <f t="shared" si="12"/>
-        <v>0.82323258064396054</v>
+        <f t="shared" si="13"/>
+        <v>0.99915490018035669</v>
       </c>
       <c r="L49" s="56">
-        <f t="shared" si="13"/>
-        <v>6.3535126464640393E-38</v>
+        <f t="shared" si="14"/>
+        <v>9.0666996502323001E-39</v>
       </c>
       <c r="M49" s="56">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="N49" s="56">
-        <f t="shared" si="15"/>
-        <v>2.1343873978107244E-38</v>
+        <f t="shared" si="16"/>
+        <v>9.6475877256394232E-42</v>
       </c>
       <c r="O49" s="57">
-        <f t="shared" si="16"/>
-        <v>8.2714359125795865E-6</v>
+        <f t="shared" si="17"/>
+        <v>1.0039016819665889E-5</v>
       </c>
       <c r="P49" s="57">
-        <f t="shared" si="17"/>
-        <v>6.2736903923717605E-5</v>
+        <f t="shared" si="18"/>
+        <v>8.9527903147937413E-6</v>
       </c>
       <c r="Q49" s="57">
-        <f t="shared" si="18"/>
-        <v>6.6073286486762687E-4</v>
-      </c>
-      <c r="R49" s="7"/>
+        <f t="shared" si="19"/>
+        <v>2.9865610542687306E-7</v>
+      </c>
+      <c r="R49" s="9">
+        <f>O49/F49</f>
+        <v>1.0039016819665889</v>
+      </c>
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
@@ -16787,45 +16817,48 @@
       <c r="F50" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G50" s="129"/>
-      <c r="H50" s="129"/>
+      <c r="G50" s="160"/>
+      <c r="H50" s="160"/>
       <c r="I50" s="55">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.552997157778905</v>
       </c>
       <c r="J50" s="55">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.4317754540220289</v>
       </c>
       <c r="K50" s="56">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.7857650342181829E-3</v>
       </c>
       <c r="L50" s="56">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.6607115936643935E-37</v>
       </c>
       <c r="M50" s="56">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="N50" s="56">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.1920175853126908E-37</v>
       </c>
       <c r="O50" s="57">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.7989996375041817E-8</v>
       </c>
       <c r="P50" s="57">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7.5644663665934365E-4</v>
       </c>
       <c r="Q50" s="57">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.9168354923060644E-2</v>
       </c>
-      <c r="R50" s="7"/>
+      <c r="R50" s="9">
+        <f t="shared" ref="R50:R68" si="20">O50/F50</f>
+        <v>2.7989996375041813E-3</v>
+      </c>
       <c r="S50" s="7"/>
       <c r="T50" s="7"/>
       <c r="U50" s="7"/>
@@ -16850,53 +16883,56 @@
         <v>83</v>
       </c>
       <c r="D51" s="90">
-        <v>7.1429999999999998</v>
+        <v>2.3724999877244022</v>
       </c>
       <c r="E51" s="90">
-        <v>9.299925</v>
+        <v>2.8974999825375303</v>
       </c>
       <c r="F51" s="91">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G51" s="129"/>
-      <c r="H51" s="129"/>
+      <c r="G51" s="160"/>
+      <c r="H51" s="160"/>
       <c r="I51" s="55">
-        <f t="shared" ref="I51:I70" si="19">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
-        <v>5.5699117487608749</v>
+        <f t="shared" ref="I51:I70" si="21">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
+        <v>0.3415531664888502</v>
       </c>
       <c r="J51" s="55">
-        <f t="shared" ref="J51:J70" si="20">IF(D51=0,"",LOG($K$21*10^D51+$K$22*10^E51+$K$20))</f>
-        <v>7.8125605305456389</v>
+        <f t="shared" ref="J51:J70" si="22">IF(D51=0,"",LOG($K$21*10^D51+$K$22*10^E51+$K$20))</f>
+        <v>1.6844884001093496</v>
       </c>
       <c r="K51" s="56">
-        <f t="shared" ref="K51:K70" si="21">IF(D51=0,"",1/(1+10^D51*$J$15/$J$14+10^E51*$J$16/$J$14+10^J51*$J$19/$J$14))</f>
-        <v>2.6793527353994627E-6</v>
+        <f t="shared" ref="K51:K70" si="23">IF(D51=0,"",1/(1+10^D51*$J$15/$J$14+10^E51*$J$16/$J$14+10^J51*$J$19/$J$14))</f>
+        <v>0.45330287581188161</v>
       </c>
       <c r="L51" s="56">
-        <f t="shared" ref="L51:L70" si="22">IF(D51=0,"",1/(1+10^I51/10^J51*$J$13/$J$19))</f>
-        <v>1.7706780274273105E-36</v>
+        <f t="shared" ref="L51:L70" si="24">IF(D51=0,"",1/(1+10^I51/10^J51*$J$13/$J$19))</f>
+        <v>2.230622353011702E-37</v>
       </c>
       <c r="M51" s="56">
-        <f t="shared" ref="M51:M70" si="23">IF(D51=0,"",1-L51)</f>
+        <f t="shared" ref="M51:M70" si="25">IF(D51=0,"",1-L51)</f>
         <v>1</v>
       </c>
       <c r="N51" s="56">
-        <f t="shared" ref="N51:N70" si="24">IF(D51=0,"",1/(1/10^E51*$J$20/$J$22+10^D51/10^E51*$J$21/$J$22+10^I51/10^E51*$J$13/$J$22+1))</f>
-        <v>1.7348446458303191E-36</v>
+        <f t="shared" ref="N51:N70" si="26">IF(D51=0,"",1/(1/10^E51*$J$20/$J$22+10^D51/10^E51*$J$21/$J$22+10^I51/10^E51*$J$13/$J$22+1))</f>
+        <v>1.1619679650215839E-37</v>
       </c>
       <c r="O51" s="57">
-        <f t="shared" ref="O51:O70" si="25">IF(D51=0,"",F51*K51*$J$7/$J$14)</f>
-        <v>2.6920817954891343E-11</v>
+        <f t="shared" ref="O51:O70" si="27">IF(D51=0,"",F51*K51*$J$7/$J$14)</f>
+        <v>4.5545642561097894E-6</v>
       </c>
       <c r="P51" s="57">
-        <f t="shared" ref="P51:P70" si="26">IF(D51=0,"",O51*10^J51)</f>
-        <v>1.7484321424679769E-3</v>
+        <f t="shared" ref="P51:P70" si="28">IF(D51=0,"",O51*10^J51)</f>
+        <v>2.2025979649048955E-4</v>
       </c>
       <c r="Q51" s="57">
-        <f t="shared" ref="Q51:Q70" si="27">IF(D51=0,"",F51*N51*$J$7/$J$22)</f>
-        <v>5.3704818259116265E-2</v>
-      </c>
-      <c r="R51" s="7"/>
+        <f t="shared" ref="Q51:Q70" si="29">IF(D51=0,"",F51*N51*$J$7/$J$22)</f>
+        <v>3.5970528274324128E-3</v>
+      </c>
+      <c r="R51" s="9">
+        <f t="shared" si="20"/>
+        <v>0.45545642561097888</v>
+      </c>
       <c r="S51" s="7"/>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
@@ -16929,45 +16965,48 @@
       <c r="F52" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G52" s="129"/>
-      <c r="H52" s="129"/>
+      <c r="G52" s="160"/>
+      <c r="H52" s="160"/>
       <c r="I52" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1.155792641235829</v>
       </c>
       <c r="J52" s="55">
+        <f t="shared" si="22"/>
+        <v>2.9263689728846836</v>
+      </c>
+      <c r="K52" s="56">
+        <f t="shared" si="23"/>
+        <v>6.9526281030514323E-2</v>
+      </c>
+      <c r="L52" s="56">
+        <f t="shared" si="24"/>
+        <v>5.9712760368179666E-37</v>
+      </c>
+      <c r="M52" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N52" s="56">
+        <f t="shared" si="26"/>
+        <v>4.4634810739111737E-37</v>
+      </c>
+      <c r="O52" s="57">
+        <f t="shared" si="27"/>
+        <v>6.9856586255860786E-7</v>
+      </c>
+      <c r="P52" s="57">
+        <f t="shared" si="28"/>
+        <v>5.8962560062320079E-4</v>
+      </c>
+      <c r="Q52" s="57">
+        <f t="shared" si="29"/>
+        <v>1.3817400909847817E-2</v>
+      </c>
+      <c r="R52" s="9">
         <f t="shared" si="20"/>
-        <v>2.9263689728846836</v>
-      </c>
-      <c r="K52" s="56">
-        <f t="shared" si="21"/>
-        <v>6.9526281030514323E-2</v>
-      </c>
-      <c r="L52" s="56">
-        <f t="shared" si="22"/>
-        <v>5.9712760368179666E-37</v>
-      </c>
-      <c r="M52" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N52" s="56">
-        <f t="shared" si="24"/>
-        <v>4.4634810739111737E-37</v>
-      </c>
-      <c r="O52" s="57">
-        <f t="shared" si="25"/>
-        <v>6.9856586255860786E-7</v>
-      </c>
-      <c r="P52" s="57">
-        <f t="shared" si="26"/>
-        <v>5.8962560062320079E-4</v>
-      </c>
-      <c r="Q52" s="57">
-        <f t="shared" si="27"/>
-        <v>1.3817400909847817E-2</v>
-      </c>
-      <c r="R52" s="7"/>
+        <v>6.9856586255860775E-2</v>
+      </c>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
@@ -17000,45 +17039,48 @@
       <c r="F53" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G53" s="129"/>
-      <c r="H53" s="129"/>
+      <c r="G53" s="160"/>
+      <c r="H53" s="160"/>
       <c r="I53" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>3.7390634769430418</v>
       </c>
       <c r="J53" s="55">
+        <f t="shared" si="22"/>
+        <v>5.6316575810820622</v>
+      </c>
+      <c r="K53" s="56">
+        <f t="shared" si="23"/>
+        <v>1.8150064128195689E-4</v>
+      </c>
+      <c r="L53" s="56">
+        <f t="shared" si="24"/>
+        <v>7.9083324971371179E-37</v>
+      </c>
+      <c r="M53" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N53" s="56">
+        <f t="shared" si="26"/>
+        <v>6.4613588561648418E-37</v>
+      </c>
+      <c r="O53" s="57">
+        <f t="shared" si="27"/>
+        <v>1.8236291392664003E-9</v>
+      </c>
+      <c r="P53" s="57">
+        <f t="shared" si="28"/>
+        <v>7.8089762888223341E-4</v>
+      </c>
+      <c r="Q53" s="57">
+        <f t="shared" si="29"/>
+        <v>2.0002142780409168E-2</v>
+      </c>
+      <c r="R53" s="9">
         <f t="shared" si="20"/>
-        <v>5.6316575810820622</v>
-      </c>
-      <c r="K53" s="56">
-        <f t="shared" si="21"/>
-        <v>1.8150064128195689E-4</v>
-      </c>
-      <c r="L53" s="56">
-        <f t="shared" si="22"/>
-        <v>7.9083324971371179E-37</v>
-      </c>
-      <c r="M53" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N53" s="56">
-        <f t="shared" si="24"/>
-        <v>6.4613588561648418E-37</v>
-      </c>
-      <c r="O53" s="57">
-        <f t="shared" si="25"/>
-        <v>1.8236291392664003E-9</v>
-      </c>
-      <c r="P53" s="57">
-        <f t="shared" si="26"/>
-        <v>7.8089762888223341E-4</v>
-      </c>
-      <c r="Q53" s="57">
-        <f t="shared" si="27"/>
-        <v>2.0002142780409168E-2</v>
-      </c>
-      <c r="R53" s="7"/>
+        <v>1.8236291392664003E-4</v>
+      </c>
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
       <c r="U53" s="7"/>
@@ -17071,45 +17113,48 @@
       <c r="F54" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G54" s="129"/>
-      <c r="H54" s="129"/>
+      <c r="G54" s="160"/>
+      <c r="H54" s="160"/>
       <c r="I54" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>3.3165609217581955</v>
       </c>
       <c r="J54" s="55">
+        <f t="shared" si="22"/>
+        <v>5.1468606681657496</v>
+      </c>
+      <c r="K54" s="56">
+        <f t="shared" si="23"/>
+        <v>4.8015418556699867E-4</v>
+      </c>
+      <c r="L54" s="56">
+        <f t="shared" si="24"/>
+        <v>6.8515773141157857E-37</v>
+      </c>
+      <c r="M54" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N54" s="56">
+        <f t="shared" si="26"/>
+        <v>5.2878170043209859E-37</v>
+      </c>
+      <c r="O54" s="57">
+        <f t="shared" si="27"/>
+        <v>4.824353004794323E-9</v>
+      </c>
+      <c r="P54" s="57">
+        <f t="shared" si="28"/>
+        <v>6.7654976325707162E-4</v>
+      </c>
+      <c r="Q54" s="57">
+        <f t="shared" si="29"/>
+        <v>1.6369261183534163E-2</v>
+      </c>
+      <c r="R54" s="9">
         <f t="shared" si="20"/>
-        <v>5.1468606681657496</v>
-      </c>
-      <c r="K54" s="56">
-        <f t="shared" si="21"/>
-        <v>4.8015418556699867E-4</v>
-      </c>
-      <c r="L54" s="56">
-        <f t="shared" si="22"/>
-        <v>6.8515773141157857E-37</v>
-      </c>
-      <c r="M54" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N54" s="56">
-        <f t="shared" si="24"/>
-        <v>5.2878170043209859E-37</v>
-      </c>
-      <c r="O54" s="57">
-        <f t="shared" si="25"/>
-        <v>4.824353004794323E-9</v>
-      </c>
-      <c r="P54" s="57">
-        <f t="shared" si="26"/>
-        <v>6.7654976325707162E-4</v>
-      </c>
-      <c r="Q54" s="57">
-        <f t="shared" si="27"/>
-        <v>1.6369261183534163E-2</v>
-      </c>
-      <c r="R54" s="7"/>
+        <v>4.8243530047943227E-4</v>
+      </c>
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
       <c r="U54" s="7"/>
@@ -17142,45 +17187,48 @@
       <c r="F55" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G55" s="129"/>
-      <c r="H55" s="129"/>
+      <c r="G55" s="160"/>
+      <c r="H55" s="160"/>
       <c r="I55" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>3.2938799134674657</v>
       </c>
       <c r="J55" s="55">
+        <f t="shared" si="22"/>
+        <v>5.1666988116250678</v>
+      </c>
+      <c r="K55" s="56">
+        <f t="shared" si="23"/>
+        <v>5.0589656117643359E-4</v>
+      </c>
+      <c r="L55" s="56">
+        <f t="shared" si="24"/>
+        <v>7.5563090916711386E-37</v>
+      </c>
+      <c r="M55" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N55" s="56">
+        <f t="shared" si="26"/>
+        <v>6.0709327965003618E-37</v>
+      </c>
+      <c r="O55" s="57">
+        <f t="shared" si="27"/>
+        <v>5.082999728815418E-9</v>
+      </c>
+      <c r="P55" s="57">
+        <f t="shared" si="28"/>
+        <v>7.4613755237572037E-4</v>
+      </c>
+      <c r="Q55" s="57">
+        <f t="shared" si="29"/>
+        <v>1.8793518098752536E-2</v>
+      </c>
+      <c r="R55" s="9">
         <f t="shared" si="20"/>
-        <v>5.1666988116250678</v>
-      </c>
-      <c r="K55" s="56">
-        <f t="shared" si="21"/>
-        <v>5.0589656117643359E-4</v>
-      </c>
-      <c r="L55" s="56">
-        <f t="shared" si="22"/>
-        <v>7.5563090916711386E-37</v>
-      </c>
-      <c r="M55" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N55" s="56">
-        <f t="shared" si="24"/>
-        <v>6.0709327965003618E-37</v>
-      </c>
-      <c r="O55" s="57">
-        <f t="shared" si="25"/>
-        <v>5.082999728815418E-9</v>
-      </c>
-      <c r="P55" s="57">
-        <f t="shared" si="26"/>
-        <v>7.4613755237572037E-4</v>
-      </c>
-      <c r="Q55" s="57">
-        <f t="shared" si="27"/>
-        <v>1.8793518098752536E-2</v>
-      </c>
-      <c r="R55" s="7"/>
+        <v>5.0829997288154175E-4</v>
+      </c>
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
@@ -17213,45 +17261,48 @@
       <c r="F56" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G56" s="129"/>
-      <c r="H56" s="129"/>
+      <c r="G56" s="160"/>
+      <c r="H56" s="160"/>
       <c r="I56" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.56442220215166938</v>
       </c>
       <c r="J56" s="55">
+        <f t="shared" si="22"/>
+        <v>2.0301330973165719</v>
+      </c>
+      <c r="K56" s="56">
+        <f t="shared" si="23"/>
+        <v>0.27134351003122564</v>
+      </c>
+      <c r="L56" s="56">
+        <f t="shared" si="24"/>
+        <v>2.9593866577889252E-37</v>
+      </c>
+      <c r="M56" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N56" s="56">
+        <f t="shared" si="26"/>
+        <v>1.5664016671934852E-37</v>
+      </c>
+      <c r="O56" s="57">
+        <f t="shared" si="27"/>
+        <v>2.7263260787881265E-6</v>
+      </c>
+      <c r="P56" s="57">
+        <f t="shared" si="28"/>
+        <v>2.9222064510434824E-4</v>
+      </c>
+      <c r="Q56" s="57">
+        <f t="shared" si="29"/>
+        <v>4.8490403483442933E-3</v>
+      </c>
+      <c r="R56" s="9">
         <f t="shared" si="20"/>
-        <v>2.0301330973165719</v>
-      </c>
-      <c r="K56" s="56">
-        <f t="shared" si="21"/>
-        <v>0.27134351003122564</v>
-      </c>
-      <c r="L56" s="56">
-        <f t="shared" si="22"/>
-        <v>2.9593866577889252E-37</v>
-      </c>
-      <c r="M56" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N56" s="56">
-        <f t="shared" si="24"/>
-        <v>1.5664016671934852E-37</v>
-      </c>
-      <c r="O56" s="57">
-        <f t="shared" si="25"/>
-        <v>2.7263260787881265E-6</v>
-      </c>
-      <c r="P56" s="57">
-        <f t="shared" si="26"/>
-        <v>2.9222064510434824E-4</v>
-      </c>
-      <c r="Q56" s="57">
-        <f t="shared" si="27"/>
-        <v>4.8490403483442933E-3</v>
-      </c>
-      <c r="R56" s="7"/>
+        <v>0.27263260787881261</v>
+      </c>
       <c r="S56" s="7"/>
       <c r="T56" s="7"/>
       <c r="U56" s="7"/>
@@ -17276,53 +17327,56 @@
         <v>89</v>
       </c>
       <c r="D57" s="90">
-        <v>7.5547280000000008</v>
+        <v>3.9841999877244016</v>
       </c>
       <c r="E57" s="90">
-        <v>9.7459910000000001</v>
+        <v>5.1901999825375293</v>
       </c>
       <c r="F57" s="91">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G57" s="129"/>
-      <c r="H57" s="129"/>
+      <c r="G57" s="160"/>
+      <c r="H57" s="160"/>
       <c r="I57" s="55">
-        <f t="shared" si="19"/>
-        <v>6.0102891918446346</v>
+        <f t="shared" si="21"/>
+        <v>1.8389468238593161</v>
       </c>
       <c r="J57" s="55">
+        <f t="shared" si="22"/>
+        <v>3.7675494433256032</v>
+      </c>
+      <c r="K57" s="56">
+        <f t="shared" si="23"/>
+        <v>1.4420981407173024E-2</v>
+      </c>
+      <c r="L57" s="56">
+        <f t="shared" si="24"/>
+        <v>8.5919835286250348E-37</v>
+      </c>
+      <c r="M57" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N57" s="56">
+        <f t="shared" si="26"/>
+        <v>7.2527130896336297E-37</v>
+      </c>
+      <c r="O57" s="57">
+        <f t="shared" si="27"/>
+        <v>1.4489492557817238E-7</v>
+      </c>
+      <c r="P57" s="57">
+        <f t="shared" si="28"/>
+        <v>8.4840382815560428E-4</v>
+      </c>
+      <c r="Q57" s="57">
+        <f t="shared" si="29"/>
+        <v>2.2451903073883901E-2</v>
+      </c>
+      <c r="R57" s="9">
         <f t="shared" si="20"/>
-        <v>8.2579578730069816</v>
-      </c>
-      <c r="K57" s="56">
-        <f t="shared" si="21"/>
-        <v>9.7196907873905555E-7</v>
-      </c>
-      <c r="L57" s="56">
-        <f t="shared" si="22"/>
-        <v>1.7912635864903517E-36</v>
-      </c>
-      <c r="M57" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N57" s="56">
-        <f t="shared" si="24"/>
-        <v>1.7577177848516138E-36</v>
-      </c>
-      <c r="O57" s="57">
-        <f t="shared" si="25"/>
-        <v>9.7658670621494198E-12</v>
-      </c>
-      <c r="P57" s="57">
-        <f t="shared" si="26"/>
-        <v>1.7687590751903493E-3</v>
-      </c>
-      <c r="Q57" s="57">
-        <f t="shared" si="27"/>
-        <v>5.4412891905426072E-2</v>
-      </c>
-      <c r="R57" s="7"/>
+        <v>1.4489492557817236E-2</v>
+      </c>
       <c r="S57" s="7"/>
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
@@ -17355,45 +17409,48 @@
       <c r="F58" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G58" s="129"/>
-      <c r="H58" s="129"/>
+      <c r="G58" s="160"/>
+      <c r="H58" s="160"/>
       <c r="I58" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1.8993925761092847</v>
       </c>
       <c r="J58" s="55">
+        <f t="shared" si="22"/>
+        <v>3.7263618048148861</v>
+      </c>
+      <c r="K58" s="56">
+        <f t="shared" si="23"/>
+        <v>1.254726483292143E-2</v>
+      </c>
+      <c r="L58" s="56">
+        <f t="shared" si="24"/>
+        <v>6.7992348934950588E-37</v>
+      </c>
+      <c r="M58" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N58" s="56">
+        <f t="shared" si="26"/>
+        <v>5.2565374483791139E-37</v>
+      </c>
+      <c r="O58" s="57">
+        <f t="shared" si="27"/>
+        <v>1.2606874337078582E-7</v>
+      </c>
+      <c r="P58" s="57">
+        <f t="shared" si="28"/>
+        <v>6.7138128151108005E-4</v>
+      </c>
+      <c r="Q58" s="57">
+        <f t="shared" si="29"/>
+        <v>1.6272430445916149E-2</v>
+      </c>
+      <c r="R58" s="9">
         <f t="shared" si="20"/>
-        <v>3.7263618048148861</v>
-      </c>
-      <c r="K58" s="56">
-        <f t="shared" si="21"/>
-        <v>1.254726483292143E-2</v>
-      </c>
-      <c r="L58" s="56">
-        <f t="shared" si="22"/>
-        <v>6.7992348934950588E-37</v>
-      </c>
-      <c r="M58" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N58" s="56">
-        <f t="shared" si="24"/>
-        <v>5.2565374483791139E-37</v>
-      </c>
-      <c r="O58" s="57">
-        <f t="shared" si="25"/>
-        <v>1.2606874337078582E-7</v>
-      </c>
-      <c r="P58" s="57">
-        <f t="shared" si="26"/>
-        <v>6.7138128151108005E-4</v>
-      </c>
-      <c r="Q58" s="57">
-        <f t="shared" si="27"/>
-        <v>1.6272430445916149E-2</v>
-      </c>
-      <c r="R58" s="7"/>
+        <v>1.2606874337078581E-2</v>
+      </c>
       <c r="S58" s="7"/>
       <c r="T58" s="7"/>
       <c r="U58" s="7"/>
@@ -17426,45 +17483,48 @@
       <c r="F59" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G59" s="129"/>
-      <c r="H59" s="129"/>
+      <c r="G59" s="160"/>
+      <c r="H59" s="160"/>
       <c r="I59" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.66933218862556854</v>
       </c>
       <c r="J59" s="55">
+        <f t="shared" si="22"/>
+        <v>2.2690120347155558</v>
+      </c>
+      <c r="K59" s="56">
+        <f t="shared" si="23"/>
+        <v>0.21311275928056553</v>
+      </c>
+      <c r="L59" s="56">
+        <f t="shared" si="24"/>
+        <v>4.0287531901071813E-37</v>
+      </c>
+      <c r="M59" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N59" s="56">
+        <f t="shared" si="26"/>
+        <v>2.624908385233338E-37</v>
+      </c>
+      <c r="O59" s="57">
+        <f t="shared" si="27"/>
+        <v>2.1412521467059969E-6</v>
+      </c>
+      <c r="P59" s="57">
+        <f t="shared" si="28"/>
+        <v>3.9781380141076848E-4</v>
+      </c>
+      <c r="Q59" s="57">
+        <f t="shared" si="29"/>
+        <v>8.1258127703023562E-3</v>
+      </c>
+      <c r="R59" s="9">
         <f t="shared" si="20"/>
-        <v>2.2690120347155558</v>
-      </c>
-      <c r="K59" s="56">
-        <f t="shared" si="21"/>
-        <v>0.21311275928056553</v>
-      </c>
-      <c r="L59" s="56">
-        <f t="shared" si="22"/>
-        <v>4.0287531901071813E-37</v>
-      </c>
-      <c r="M59" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N59" s="56">
-        <f t="shared" si="24"/>
-        <v>2.624908385233338E-37</v>
-      </c>
-      <c r="O59" s="57">
-        <f t="shared" si="25"/>
-        <v>2.1412521467059969E-6</v>
-      </c>
-      <c r="P59" s="57">
-        <f t="shared" si="26"/>
-        <v>3.9781380141076848E-4</v>
-      </c>
-      <c r="Q59" s="57">
-        <f t="shared" si="27"/>
-        <v>8.1258127703023562E-3</v>
-      </c>
-      <c r="R59" s="7"/>
+        <v>0.21412521467059967</v>
+      </c>
       <c r="S59" s="7"/>
       <c r="T59" s="7"/>
       <c r="U59" s="7"/>
@@ -17489,53 +17549,56 @@
         <v>94</v>
       </c>
       <c r="D60" s="48">
-        <v>-2.3039999999996397E-3</v>
+        <v>3.03</v>
       </c>
       <c r="E60" s="48">
-        <v>-1.314813</v>
+        <v>3.96</v>
       </c>
       <c r="F60" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G60" s="129"/>
-      <c r="H60" s="129"/>
+      <c r="G60" s="160"/>
+      <c r="H60" s="160"/>
       <c r="I60" s="55">
-        <f t="shared" si="19"/>
-        <v>-7.429644403464382E-5</v>
+        <f t="shared" si="21"/>
+        <v>0.86355706001910959</v>
       </c>
       <c r="J60" s="55">
+        <f t="shared" si="22"/>
+        <v>2.5945087996693723</v>
+      </c>
+      <c r="K60" s="56">
+        <f t="shared" si="23"/>
+        <v>0.13626508164202661</v>
+      </c>
+      <c r="L60" s="56">
+        <f t="shared" si="24"/>
+        <v>5.450577962533167E-37</v>
+      </c>
+      <c r="M60" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N60" s="56">
+        <f t="shared" si="26"/>
+        <v>4.0335763210518438E-37</v>
+      </c>
+      <c r="O60" s="57">
+        <f t="shared" si="27"/>
+        <v>1.3691244933998918E-6</v>
+      </c>
+      <c r="P60" s="57">
+        <f t="shared" si="28"/>
+        <v>5.3820997138407322E-4</v>
+      </c>
+      <c r="Q60" s="57">
+        <f t="shared" si="29"/>
+        <v>1.2486563784083717E-2</v>
+      </c>
+      <c r="R60" s="9">
         <f t="shared" si="20"/>
-        <v>-1.3610239300554092E-2</v>
-      </c>
-      <c r="K60" s="56">
-        <f t="shared" si="21"/>
-        <v>0.99544194622158988</v>
-      </c>
-      <c r="L60" s="56">
-        <f t="shared" si="22"/>
-        <v>9.8164593715857243E-39</v>
-      </c>
-      <c r="M60" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N60" s="56">
-        <f t="shared" si="24"/>
-        <v>1.5649794361852636E-41</v>
-      </c>
-      <c r="O60" s="57">
-        <f t="shared" si="25"/>
-        <v>1.000171088518468E-5</v>
-      </c>
-      <c r="P60" s="57">
-        <f t="shared" si="26"/>
-        <v>9.6931304419295731E-6</v>
-      </c>
-      <c r="Q60" s="57">
-        <f t="shared" si="27"/>
-        <v>4.8446376107272627E-7</v>
-      </c>
-      <c r="R60" s="7"/>
+        <v>0.13691244933998917</v>
+      </c>
       <c r="S60" s="7"/>
       <c r="T60" s="7"/>
       <c r="U60" s="7"/>
@@ -17568,45 +17631,48 @@
       <c r="F61" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G61" s="129"/>
-      <c r="H61" s="129"/>
+      <c r="G61" s="160"/>
+      <c r="H61" s="160"/>
       <c r="I61" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.98830104104276184</v>
       </c>
       <c r="J61" s="55">
+        <f t="shared" si="22"/>
+        <v>2.5373705838993215</v>
+      </c>
+      <c r="K61" s="56">
+        <f t="shared" si="23"/>
+        <v>0.10224465167750552</v>
+      </c>
+      <c r="L61" s="56">
+        <f t="shared" si="24"/>
+        <v>3.5855877808014127E-37</v>
+      </c>
+      <c r="M61" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N61" s="56">
+        <f t="shared" si="26"/>
+        <v>1.8855206703974334E-37</v>
+      </c>
+      <c r="O61" s="57">
+        <f t="shared" si="27"/>
+        <v>1.0273039522961621E-6</v>
+      </c>
+      <c r="P61" s="57">
+        <f t="shared" si="28"/>
+        <v>3.5405403063042021E-4</v>
+      </c>
+      <c r="Q61" s="57">
+        <f t="shared" si="29"/>
+        <v>5.836922929720669E-3</v>
+      </c>
+      <c r="R61" s="9">
         <f t="shared" si="20"/>
-        <v>2.5373705838993215</v>
-      </c>
-      <c r="K61" s="56">
-        <f t="shared" si="21"/>
-        <v>0.10224465167750552</v>
-      </c>
-      <c r="L61" s="56">
-        <f t="shared" si="22"/>
-        <v>3.5855877808014127E-37</v>
-      </c>
-      <c r="M61" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N61" s="56">
-        <f t="shared" si="24"/>
-        <v>1.8855206703974334E-37</v>
-      </c>
-      <c r="O61" s="57">
-        <f t="shared" si="25"/>
-        <v>1.0273039522961621E-6</v>
-      </c>
-      <c r="P61" s="57">
-        <f t="shared" si="26"/>
-        <v>3.5405403063042021E-4</v>
-      </c>
-      <c r="Q61" s="57">
-        <f t="shared" si="27"/>
-        <v>5.836922929720669E-3</v>
-      </c>
-      <c r="R61" s="7"/>
+        <v>0.1027303952296162</v>
+      </c>
       <c r="S61" s="7"/>
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
@@ -17639,45 +17705,48 @@
       <c r="F62" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G62" s="129"/>
-      <c r="H62" s="129"/>
+      <c r="G62" s="160"/>
+      <c r="H62" s="160"/>
       <c r="I62" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1.0720640142200413</v>
       </c>
       <c r="J62" s="55">
+        <f t="shared" si="22"/>
+        <v>2.6177093589669362</v>
+      </c>
+      <c r="K62" s="56">
+        <f t="shared" si="23"/>
+        <v>8.4309716036386609E-2</v>
+      </c>
+      <c r="L62" s="56">
+        <f t="shared" si="24"/>
+        <v>3.5574283444923687E-37</v>
+      </c>
+      <c r="M62" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N62" s="56">
+        <f t="shared" si="26"/>
+        <v>1.8142800482407409E-37</v>
+      </c>
+      <c r="O62" s="57">
+        <f t="shared" si="27"/>
+        <v>8.4710254355731964E-7</v>
+      </c>
+      <c r="P62" s="57">
+        <f t="shared" si="28"/>
+        <v>3.5127346506209683E-4</v>
+      </c>
+      <c r="Q62" s="57">
+        <f t="shared" si="29"/>
+        <v>5.6163864871759594E-3</v>
+      </c>
+      <c r="R62" s="9">
         <f t="shared" si="20"/>
-        <v>2.6177093589669362</v>
-      </c>
-      <c r="K62" s="56">
-        <f t="shared" si="21"/>
-        <v>8.4309716036386609E-2</v>
-      </c>
-      <c r="L62" s="56">
-        <f t="shared" si="22"/>
-        <v>3.5574283444923687E-37</v>
-      </c>
-      <c r="M62" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N62" s="56">
-        <f t="shared" si="24"/>
-        <v>1.8142800482407409E-37</v>
-      </c>
-      <c r="O62" s="57">
-        <f t="shared" si="25"/>
-        <v>8.4710254355731964E-7</v>
-      </c>
-      <c r="P62" s="57">
-        <f t="shared" si="26"/>
-        <v>3.5127346506209683E-4</v>
-      </c>
-      <c r="Q62" s="57">
-        <f t="shared" si="27"/>
-        <v>5.6163864871759594E-3</v>
-      </c>
-      <c r="R62" s="7"/>
+        <v>8.4710254355731956E-2</v>
+      </c>
       <c r="S62" s="7"/>
       <c r="T62" s="7"/>
       <c r="U62" s="7"/>
@@ -17710,45 +17779,48 @@
       <c r="F63" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G63" s="129"/>
-      <c r="H63" s="129"/>
+      <c r="G63" s="160"/>
+      <c r="H63" s="160"/>
       <c r="I63" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2.2754629671517499</v>
       </c>
       <c r="J63" s="55">
+        <f t="shared" si="22"/>
+        <v>4.2142112253027877</v>
+      </c>
+      <c r="K63" s="56">
+        <f t="shared" si="23"/>
+        <v>5.2781128755291949E-3</v>
+      </c>
+      <c r="L63" s="56">
+        <f t="shared" si="24"/>
+        <v>8.7950654254575997E-37</v>
+      </c>
+      <c r="M63" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N63" s="56">
+        <f t="shared" si="26"/>
+        <v>7.4579998741856271E-37</v>
+      </c>
+      <c r="O63" s="57">
+        <f t="shared" si="27"/>
+        <v>5.3031881166742035E-8</v>
+      </c>
+      <c r="P63" s="57">
+        <f t="shared" si="28"/>
+        <v>8.6845687622393746E-4</v>
+      </c>
+      <c r="Q63" s="57">
+        <f t="shared" si="29"/>
+        <v>2.3087400291566276E-2</v>
+      </c>
+      <c r="R63" s="9">
         <f t="shared" si="20"/>
-        <v>4.2142112253027877</v>
-      </c>
-      <c r="K63" s="56">
-        <f t="shared" si="21"/>
-        <v>5.2781128755291949E-3</v>
-      </c>
-      <c r="L63" s="56">
-        <f t="shared" si="22"/>
-        <v>8.7950654254575997E-37</v>
-      </c>
-      <c r="M63" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N63" s="56">
-        <f t="shared" si="24"/>
-        <v>7.4579998741856271E-37</v>
-      </c>
-      <c r="O63" s="57">
-        <f t="shared" si="25"/>
-        <v>5.3031881166742035E-8</v>
-      </c>
-      <c r="P63" s="57">
-        <f t="shared" si="26"/>
-        <v>8.6845687622393746E-4</v>
-      </c>
-      <c r="Q63" s="57">
-        <f t="shared" si="27"/>
-        <v>2.3087400291566276E-2</v>
-      </c>
-      <c r="R63" s="7"/>
+        <v>5.3031881166742028E-3</v>
+      </c>
       <c r="S63" s="7"/>
       <c r="T63" s="7"/>
       <c r="U63" s="7"/>
@@ -17781,45 +17853,48 @@
       <c r="F64" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G64" s="129"/>
-      <c r="H64" s="129"/>
+      <c r="G64" s="160"/>
+      <c r="H64" s="160"/>
       <c r="I64" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2.0741209065073765</v>
       </c>
       <c r="J64" s="55">
+        <f t="shared" si="22"/>
+        <v>3.9176541849923314</v>
+      </c>
+      <c r="K64" s="56">
+        <f t="shared" si="23"/>
+        <v>8.3911355026446213E-3</v>
+      </c>
+      <c r="L64" s="56">
+        <f t="shared" si="24"/>
+        <v>7.0635674208724982E-37</v>
+      </c>
+      <c r="M64" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N64" s="56">
+        <f t="shared" si="26"/>
+        <v>5.5409908416545747E-37</v>
+      </c>
+      <c r="O64" s="57">
+        <f t="shared" si="27"/>
+        <v>8.4310000813626648E-8</v>
+      </c>
+      <c r="P64" s="57">
+        <f t="shared" si="28"/>
+        <v>6.9748244050258919E-4</v>
+      </c>
+      <c r="Q64" s="57">
+        <f t="shared" si="29"/>
+        <v>1.7153000232136749E-2</v>
+      </c>
+      <c r="R64" s="9">
         <f t="shared" si="20"/>
-        <v>3.9176541849923314</v>
-      </c>
-      <c r="K64" s="56">
-        <f t="shared" si="21"/>
-        <v>8.3911355026446213E-3</v>
-      </c>
-      <c r="L64" s="56">
-        <f t="shared" si="22"/>
-        <v>7.0635674208724982E-37</v>
-      </c>
-      <c r="M64" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N64" s="56">
-        <f t="shared" si="24"/>
-        <v>5.5409908416545747E-37</v>
-      </c>
-      <c r="O64" s="57">
-        <f t="shared" si="25"/>
-        <v>8.4310000813626648E-8</v>
-      </c>
-      <c r="P64" s="57">
-        <f t="shared" si="26"/>
-        <v>6.9748244050258919E-4</v>
-      </c>
-      <c r="Q64" s="57">
-        <f t="shared" si="27"/>
-        <v>1.7153000232136749E-2</v>
-      </c>
-      <c r="R64" s="7"/>
+        <v>8.4310000813626641E-3</v>
+      </c>
       <c r="S64" s="7"/>
       <c r="T64" s="7"/>
       <c r="U64" s="7"/>
@@ -17852,45 +17927,48 @@
       <c r="F65" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G65" s="129"/>
-      <c r="H65" s="129"/>
+      <c r="G65" s="160"/>
+      <c r="H65" s="160"/>
       <c r="I65" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.62172127754097484</v>
       </c>
       <c r="J65" s="55">
+        <f t="shared" si="22"/>
+        <v>2.2124774852203832</v>
+      </c>
+      <c r="K65" s="56">
+        <f t="shared" si="23"/>
+        <v>0.23780466135330647</v>
+      </c>
+      <c r="L65" s="56">
+        <f t="shared" si="24"/>
+        <v>3.9468173075545129E-37</v>
+      </c>
+      <c r="M65" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N65" s="56">
+        <f t="shared" si="26"/>
+        <v>2.5888689175055068E-37</v>
+      </c>
+      <c r="O65" s="57">
+        <f t="shared" si="27"/>
+        <v>2.3893442294982091E-6</v>
+      </c>
+      <c r="P65" s="57">
+        <f t="shared" si="28"/>
+        <v>3.8972315316995238E-4</v>
+      </c>
+      <c r="Q65" s="57">
+        <f t="shared" si="29"/>
+        <v>8.0142469843323908E-3</v>
+      </c>
+      <c r="R65" s="9">
         <f t="shared" si="20"/>
-        <v>2.2124774852203832</v>
-      </c>
-      <c r="K65" s="56">
-        <f t="shared" si="21"/>
-        <v>0.23780466135330647</v>
-      </c>
-      <c r="L65" s="56">
-        <f t="shared" si="22"/>
-        <v>3.9468173075545129E-37</v>
-      </c>
-      <c r="M65" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N65" s="56">
-        <f t="shared" si="24"/>
-        <v>2.5888689175055068E-37</v>
-      </c>
-      <c r="O65" s="57">
-        <f t="shared" si="25"/>
-        <v>2.3893442294982091E-6</v>
-      </c>
-      <c r="P65" s="57">
-        <f t="shared" si="26"/>
-        <v>3.8972315316995238E-4</v>
-      </c>
-      <c r="Q65" s="57">
-        <f t="shared" si="27"/>
-        <v>8.0142469843323908E-3</v>
-      </c>
-      <c r="R65" s="7"/>
+        <v>0.2389344229498209</v>
+      </c>
       <c r="S65" s="7"/>
       <c r="T65" s="7"/>
       <c r="U65" s="7"/>
@@ -17923,45 +18001,48 @@
       <c r="F66" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G66" s="129"/>
-      <c r="H66" s="129"/>
+      <c r="G66" s="160"/>
+      <c r="H66" s="160"/>
       <c r="I66" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2.2151248995259314</v>
       </c>
       <c r="J66" s="55">
+        <f t="shared" si="22"/>
+        <v>3.9383630025707501</v>
+      </c>
+      <c r="K66" s="56">
+        <f t="shared" si="23"/>
+        <v>6.0648035975778523E-3</v>
+      </c>
+      <c r="L66" s="56">
+        <f t="shared" si="24"/>
+        <v>5.3546232497166912E-37</v>
+      </c>
+      <c r="M66" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N66" s="56">
+        <f t="shared" si="26"/>
+        <v>3.6369257881814162E-37</v>
+      </c>
+      <c r="O66" s="57">
+        <f t="shared" si="27"/>
+        <v>6.0936162463962299E-8</v>
+      </c>
+      <c r="P66" s="57">
+        <f t="shared" si="28"/>
+        <v>5.2873505265176317E-4</v>
+      </c>
+      <c r="Q66" s="57">
+        <f t="shared" si="29"/>
+        <v>1.1258670276074963E-2</v>
+      </c>
+      <c r="R66" s="9">
         <f t="shared" si="20"/>
-        <v>3.9383630025707501</v>
-      </c>
-      <c r="K66" s="56">
-        <f t="shared" si="21"/>
-        <v>6.0648035975778523E-3</v>
-      </c>
-      <c r="L66" s="56">
-        <f t="shared" si="22"/>
-        <v>5.3546232497166912E-37</v>
-      </c>
-      <c r="M66" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N66" s="56">
-        <f t="shared" si="24"/>
-        <v>3.6369257881814162E-37</v>
-      </c>
-      <c r="O66" s="57">
-        <f t="shared" si="25"/>
-        <v>6.0936162463962299E-8</v>
-      </c>
-      <c r="P66" s="57">
-        <f t="shared" si="26"/>
-        <v>5.2873505265176317E-4</v>
-      </c>
-      <c r="Q66" s="57">
-        <f t="shared" si="27"/>
-        <v>1.1258670276074963E-2</v>
-      </c>
-      <c r="R66" s="7"/>
+        <v>6.0936162463962294E-3</v>
+      </c>
       <c r="S66" s="7"/>
       <c r="T66" s="7"/>
       <c r="U66" s="7"/>
@@ -17994,45 +18075,48 @@
       <c r="F67" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G67" s="129"/>
-      <c r="H67" s="129"/>
+      <c r="G67" s="160"/>
+      <c r="H67" s="160"/>
       <c r="I67" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.56702977498764862</v>
       </c>
       <c r="J67" s="55">
+        <f t="shared" si="22"/>
+        <v>2.1274423042031239</v>
+      </c>
+      <c r="K67" s="56">
+        <f t="shared" si="23"/>
+        <v>0.26971920181373416</v>
+      </c>
+      <c r="L67" s="56">
+        <f t="shared" si="24"/>
+        <v>3.6804705376746659E-37</v>
+      </c>
+      <c r="M67" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N67" s="56">
+        <f t="shared" si="26"/>
+        <v>2.3640113855495875E-37</v>
+      </c>
+      <c r="O67" s="57">
+        <f t="shared" si="27"/>
+        <v>2.7100058290322827E-6</v>
+      </c>
+      <c r="P67" s="57">
+        <f t="shared" si="28"/>
+        <v>3.6342310051853575E-4</v>
+      </c>
+      <c r="Q67" s="57">
+        <f t="shared" si="29"/>
+        <v>7.3181654696612957E-3</v>
+      </c>
+      <c r="R67" s="9">
         <f t="shared" si="20"/>
-        <v>2.1274423042031239</v>
-      </c>
-      <c r="K67" s="56">
-        <f t="shared" si="21"/>
-        <v>0.26971920181373416</v>
-      </c>
-      <c r="L67" s="56">
-        <f t="shared" si="22"/>
-        <v>3.6804705376746659E-37</v>
-      </c>
-      <c r="M67" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N67" s="56">
-        <f t="shared" si="24"/>
-        <v>2.3640113855495875E-37</v>
-      </c>
-      <c r="O67" s="57">
-        <f t="shared" si="25"/>
-        <v>2.7100058290322827E-6</v>
-      </c>
-      <c r="P67" s="57">
-        <f t="shared" si="26"/>
-        <v>3.6342310051853575E-4</v>
-      </c>
-      <c r="Q67" s="57">
-        <f t="shared" si="27"/>
-        <v>7.3181654696612957E-3</v>
-      </c>
-      <c r="R67" s="7"/>
+        <v>0.27100058290322826</v>
+      </c>
       <c r="S67" s="7"/>
       <c r="T67" s="7"/>
       <c r="U67" s="7"/>
@@ -18065,45 +18149,48 @@
       <c r="F68" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G68" s="129"/>
-      <c r="H68" s="129"/>
+      <c r="G68" s="160"/>
+      <c r="H68" s="160"/>
       <c r="I68" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1.5670237821495228</v>
       </c>
       <c r="J68" s="55">
+        <f t="shared" si="22"/>
+        <v>3.1028564185767968</v>
+      </c>
+      <c r="K68" s="56">
+        <f t="shared" si="23"/>
+        <v>2.6972292370000157E-2</v>
+      </c>
+      <c r="L68" s="56">
+        <f t="shared" si="24"/>
+        <v>3.477950949596983E-37</v>
+      </c>
+      <c r="M68" s="56">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="N68" s="56">
+        <f t="shared" si="26"/>
+        <v>1.5982457443126468E-37</v>
+      </c>
+      <c r="O68" s="57">
+        <f t="shared" si="27"/>
+        <v>2.7100432247142062E-7</v>
+      </c>
+      <c r="P68" s="57">
+        <f t="shared" si="28"/>
+        <v>3.4342557686998907E-4</v>
+      </c>
+      <c r="Q68" s="57">
+        <f t="shared" si="29"/>
+        <v>4.9476186491981631E-3</v>
+      </c>
+      <c r="R68" s="9">
         <f t="shared" si="20"/>
-        <v>3.1028564185767968</v>
-      </c>
-      <c r="K68" s="56">
-        <f t="shared" si="21"/>
-        <v>2.6972292370000157E-2</v>
-      </c>
-      <c r="L68" s="56">
-        <f t="shared" si="22"/>
-        <v>3.477950949596983E-37</v>
-      </c>
-      <c r="M68" s="56">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="N68" s="56">
-        <f t="shared" si="24"/>
-        <v>1.5982457443126468E-37</v>
-      </c>
-      <c r="O68" s="57">
-        <f t="shared" si="25"/>
-        <v>2.7100432247142062E-7</v>
-      </c>
-      <c r="P68" s="57">
-        <f t="shared" si="26"/>
-        <v>3.4342557686998907E-4</v>
-      </c>
-      <c r="Q68" s="57">
-        <f t="shared" si="27"/>
-        <v>4.9476186491981631E-3</v>
-      </c>
-      <c r="R68" s="7"/>
+        <v>2.7100432247142061E-2</v>
+      </c>
       <c r="S68" s="7"/>
       <c r="T68" s="7"/>
       <c r="U68" s="7"/>
@@ -18126,42 +18213,42 @@
       <c r="D69" s="48"/>
       <c r="E69" s="48"/>
       <c r="F69" s="58"/>
-      <c r="G69" s="129"/>
-      <c r="H69" s="129"/>
+      <c r="G69" s="160"/>
+      <c r="H69" s="160"/>
       <c r="I69" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="J69" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K69" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="L69" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="M69" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="N69" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="O69" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="P69" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="Q69" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="R69" s="7"/>
@@ -18187,42 +18274,42 @@
       <c r="D70" s="48"/>
       <c r="E70" s="48"/>
       <c r="F70" s="58"/>
-      <c r="G70" s="129"/>
-      <c r="H70" s="129"/>
+      <c r="G70" s="160"/>
+      <c r="H70" s="160"/>
       <c r="I70" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="J70" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K70" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="L70" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="M70" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="N70" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="O70" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="P70" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="Q70" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="R70" s="7"/>
@@ -18248,42 +18335,42 @@
       <c r="D71" s="48"/>
       <c r="E71" s="48"/>
       <c r="F71" s="58"/>
-      <c r="G71" s="129"/>
-      <c r="H71" s="129"/>
+      <c r="G71" s="160"/>
+      <c r="H71" s="160"/>
       <c r="I71" s="55" t="str">
-        <f t="shared" ref="I71:I122" si="28">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
+        <f t="shared" ref="I71:I122" si="30">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
         <v/>
       </c>
       <c r="J71" s="55" t="str">
-        <f t="shared" ref="J71:J122" si="29">IF(D71=0,"",LOG($K$21*10^D71+$K$22*10^E71+$K$20))</f>
+        <f t="shared" ref="J71:J122" si="31">IF(D71=0,"",LOG($K$21*10^D71+$K$22*10^E71+$K$20))</f>
         <v/>
       </c>
       <c r="K71" s="56" t="str">
-        <f t="shared" ref="K71:K122" si="30">IF(D71=0,"",1/(1+10^D71*$J$15/$J$14+10^E71*$J$16/$J$14+10^J71*$J$19/$J$14))</f>
+        <f t="shared" ref="K71:K122" si="32">IF(D71=0,"",1/(1+10^D71*$J$15/$J$14+10^E71*$J$16/$J$14+10^J71*$J$19/$J$14))</f>
         <v/>
       </c>
       <c r="L71" s="56" t="str">
-        <f t="shared" ref="L71:L122" si="31">IF(D71=0,"",1/(1+10^I71/10^J71*$J$13/$J$19))</f>
+        <f t="shared" ref="L71:L122" si="33">IF(D71=0,"",1/(1+10^I71/10^J71*$J$13/$J$19))</f>
         <v/>
       </c>
       <c r="M71" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N71" s="56" t="str">
-        <f t="shared" ref="N71:N122" si="32">IF(D71=0,"",1/(1/10^E71*$J$20/$J$22+10^D71/10^E71*$J$21/$J$22+10^I71/10^E71*$J$13/$J$22+1))</f>
+        <f t="shared" ref="N71:N122" si="34">IF(D71=0,"",1/(1/10^E71*$J$20/$J$22+10^D71/10^E71*$J$21/$J$22+10^I71/10^E71*$J$13/$J$22+1))</f>
         <v/>
       </c>
       <c r="O71" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P71" s="57" t="str">
-        <f t="shared" ref="P71:P122" si="33">IF(D71=0,"",O71*10^J71)</f>
+        <f t="shared" ref="P71:P122" si="35">IF(D71=0,"",O71*10^J71)</f>
         <v/>
       </c>
       <c r="Q71" s="57" t="str">
-        <f t="shared" ref="Q71:Q122" si="34">IF(D71=0,"",F71*N71*$J$7/$J$22)</f>
+        <f t="shared" ref="Q71:Q122" si="36">IF(D71=0,"",F71*N71*$J$7/$J$22)</f>
         <v/>
       </c>
       <c r="R71" s="7"/>
@@ -18309,42 +18396,42 @@
       <c r="D72" s="48"/>
       <c r="E72" s="48"/>
       <c r="F72" s="58"/>
-      <c r="G72" s="129"/>
-      <c r="H72" s="129"/>
+      <c r="G72" s="160"/>
+      <c r="H72" s="160"/>
       <c r="I72" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J72" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K72" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L72" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M72" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N72" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O72" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P72" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q72" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R72" s="7"/>
@@ -18370,42 +18457,42 @@
       <c r="D73" s="48"/>
       <c r="E73" s="48"/>
       <c r="F73" s="58"/>
-      <c r="G73" s="129"/>
-      <c r="H73" s="129"/>
+      <c r="G73" s="160"/>
+      <c r="H73" s="160"/>
       <c r="I73" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J73" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K73" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L73" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M73" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N73" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O73" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P73" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q73" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R73" s="7"/>
@@ -18431,42 +18518,42 @@
       <c r="D74" s="48"/>
       <c r="E74" s="48"/>
       <c r="F74" s="58"/>
-      <c r="G74" s="129"/>
-      <c r="H74" s="129"/>
+      <c r="G74" s="160"/>
+      <c r="H74" s="160"/>
       <c r="I74" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J74" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K74" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L74" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M74" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N74" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O74" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P74" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q74" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R74" s="7"/>
@@ -18492,42 +18579,42 @@
       <c r="D75" s="48"/>
       <c r="E75" s="48"/>
       <c r="F75" s="58"/>
-      <c r="G75" s="129"/>
-      <c r="H75" s="129"/>
+      <c r="G75" s="160"/>
+      <c r="H75" s="160"/>
       <c r="I75" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J75" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K75" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L75" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M75" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N75" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O75" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P75" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q75" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R75" s="7"/>
@@ -18553,42 +18640,42 @@
       <c r="D76" s="48"/>
       <c r="E76" s="48"/>
       <c r="F76" s="58"/>
-      <c r="G76" s="129"/>
-      <c r="H76" s="129"/>
+      <c r="G76" s="160"/>
+      <c r="H76" s="160"/>
       <c r="I76" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J76" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K76" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L76" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M76" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N76" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O76" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P76" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q76" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R76" s="7"/>
@@ -18614,42 +18701,42 @@
       <c r="D77" s="48"/>
       <c r="E77" s="48"/>
       <c r="F77" s="58"/>
-      <c r="G77" s="129"/>
-      <c r="H77" s="129"/>
+      <c r="G77" s="160"/>
+      <c r="H77" s="160"/>
       <c r="I77" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J77" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K77" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L77" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M77" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N77" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O77" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P77" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q77" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R77" s="7"/>
@@ -18678,39 +18765,39 @@
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J78" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K78" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L78" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M78" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N78" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O78" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P78" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q78" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R78" s="7"/>
@@ -18739,39 +18826,39 @@
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
       <c r="I79" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J79" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K79" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L79" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M79" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N79" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O79" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P79" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q79" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R79" s="7"/>
@@ -18800,39 +18887,39 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J80" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K80" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L80" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M80" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N80" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O80" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P80" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q80" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R80" s="7"/>
@@ -18861,39 +18948,39 @@
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J81" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K81" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L81" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M81" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N81" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O81" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P81" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q81" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R81" s="7"/>
@@ -18922,39 +19009,39 @@
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J82" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K82" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L82" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M82" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N82" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O82" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P82" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q82" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R82" s="7"/>
@@ -18983,39 +19070,39 @@
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J83" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K83" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L83" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M83" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N83" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O83" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P83" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q83" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R83" s="7"/>
@@ -19044,39 +19131,39 @@
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J84" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K84" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L84" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M84" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N84" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O84" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P84" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q84" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R84" s="7"/>
@@ -19105,39 +19192,39 @@
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J85" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K85" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L85" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M85" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N85" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O85" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P85" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q85" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R85" s="7"/>
@@ -19166,39 +19253,39 @@
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
       <c r="I86" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J86" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K86" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L86" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M86" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N86" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O86" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P86" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q86" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R86" s="7"/>
@@ -19227,39 +19314,39 @@
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
       <c r="I87" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J87" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K87" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L87" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M87" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N87" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O87" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P87" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q87" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R87" s="7"/>
@@ -19288,39 +19375,39 @@
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
       <c r="I88" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J88" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K88" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L88" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M88" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N88" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O88" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P88" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q88" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R88" s="7"/>
@@ -19349,39 +19436,39 @@
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J89" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K89" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L89" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M89" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N89" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O89" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P89" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q89" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R89" s="7"/>
@@ -19410,39 +19497,39 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J90" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K90" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L90" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M90" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N90" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O90" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P90" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q90" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R90" s="7"/>
@@ -19471,39 +19558,39 @@
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J91" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K91" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L91" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M91" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N91" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O91" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P91" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q91" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R91" s="7"/>
@@ -19532,39 +19619,39 @@
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J92" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K92" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L92" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M92" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N92" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O92" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P92" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q92" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R92" s="7"/>
@@ -19593,39 +19680,39 @@
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
       <c r="I93" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J93" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K93" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L93" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M93" s="56" t="str">
-        <f t="shared" ref="M93:M127" si="35">IF(D93=0,"",1-L93)</f>
+        <f t="shared" ref="M93:M127" si="37">IF(D93=0,"",1-L93)</f>
         <v/>
       </c>
       <c r="N93" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O93" s="57" t="str">
-        <f t="shared" ref="O93:O127" si="36">IF(D93=0,"",F93*K93*$J$7/$J$14)</f>
+        <f t="shared" ref="O93:O127" si="38">IF(D93=0,"",F93*K93*$J$7/$J$14)</f>
         <v/>
       </c>
       <c r="P93" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q93" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R93" s="7"/>
@@ -19654,39 +19741,39 @@
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
       <c r="I94" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J94" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K94" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L94" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M94" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N94" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O94" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P94" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N94" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O94" s="57" t="str">
+      <c r="Q94" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P94" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q94" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R94" s="7"/>
@@ -19715,39 +19802,39 @@
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J95" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K95" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L95" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M95" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N95" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O95" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P95" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N95" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O95" s="57" t="str">
+      <c r="Q95" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P95" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q95" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R95" s="7"/>
@@ -19776,39 +19863,39 @@
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J96" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K96" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L96" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M96" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N96" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O96" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P96" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N96" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O96" s="57" t="str">
+      <c r="Q96" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P96" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q96" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R96" s="7"/>
@@ -19837,39 +19924,39 @@
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J97" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K97" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L97" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M97" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N97" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O97" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P97" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N97" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O97" s="57" t="str">
+      <c r="Q97" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P97" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q97" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R97" s="7"/>
@@ -19898,39 +19985,39 @@
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J98" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K98" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L98" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M98" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N98" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O98" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P98" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N98" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O98" s="57" t="str">
+      <c r="Q98" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P98" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q98" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R98" s="7"/>
@@ -19959,39 +20046,39 @@
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
       <c r="I99" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J99" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K99" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L99" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M99" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N99" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O99" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P99" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N99" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O99" s="57" t="str">
+      <c r="Q99" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P99" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q99" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R99" s="7"/>
@@ -20020,39 +20107,39 @@
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J100" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K100" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L100" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M100" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N100" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O100" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P100" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N100" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O100" s="57" t="str">
+      <c r="Q100" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P100" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q100" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R100" s="7"/>
@@ -20081,39 +20168,39 @@
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
       <c r="I101" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J101" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K101" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L101" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M101" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N101" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O101" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P101" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N101" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O101" s="57" t="str">
+      <c r="Q101" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P101" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q101" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R101" s="7"/>
@@ -20142,39 +20229,39 @@
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J102" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K102" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L102" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M102" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N102" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O102" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P102" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N102" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O102" s="57" t="str">
+      <c r="Q102" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P102" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q102" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R102" s="7"/>
@@ -20203,39 +20290,39 @@
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J103" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K103" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L103" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M103" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N103" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O103" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P103" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N103" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O103" s="57" t="str">
+      <c r="Q103" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P103" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q103" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R103" s="7"/>
@@ -20264,39 +20351,39 @@
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J104" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K104" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L104" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M104" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N104" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O104" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P104" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N104" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O104" s="57" t="str">
+      <c r="Q104" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P104" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q104" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R104" s="7"/>
@@ -20325,39 +20412,39 @@
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J105" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K105" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L105" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M105" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N105" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O105" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P105" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N105" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O105" s="57" t="str">
+      <c r="Q105" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P105" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q105" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R105" s="7"/>
@@ -20386,39 +20473,39 @@
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J106" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K106" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L106" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M106" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N106" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O106" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P106" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N106" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O106" s="57" t="str">
+      <c r="Q106" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P106" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q106" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R106" s="7"/>
@@ -20447,39 +20534,39 @@
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
       <c r="I107" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J107" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K107" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L107" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M107" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N107" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O107" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P107" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N107" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O107" s="57" t="str">
+      <c r="Q107" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P107" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q107" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R107" s="7"/>
@@ -20508,39 +20595,39 @@
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J108" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K108" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L108" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M108" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N108" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O108" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P108" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N108" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O108" s="57" t="str">
+      <c r="Q108" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P108" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q108" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R108" s="7"/>
@@ -20569,39 +20656,39 @@
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
       <c r="I109" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J109" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K109" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L109" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M109" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N109" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O109" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P109" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N109" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O109" s="57" t="str">
+      <c r="Q109" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P109" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q109" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R109" s="7"/>
@@ -20630,39 +20717,39 @@
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
       <c r="I110" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J110" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K110" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L110" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M110" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N110" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O110" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P110" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N110" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O110" s="57" t="str">
+      <c r="Q110" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P110" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q110" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R110" s="7"/>
@@ -20691,39 +20778,39 @@
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
       <c r="I111" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J111" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K111" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L111" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M111" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N111" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O111" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P111" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N111" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O111" s="57" t="str">
+      <c r="Q111" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P111" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q111" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R111" s="7"/>
@@ -20752,39 +20839,39 @@
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
       <c r="I112" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J112" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K112" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L112" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M112" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N112" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O112" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P112" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N112" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O112" s="57" t="str">
+      <c r="Q112" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P112" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q112" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R112" s="7"/>
@@ -20813,39 +20900,39 @@
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
       <c r="I113" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J113" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K113" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L113" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M113" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N113" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O113" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P113" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N113" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O113" s="57" t="str">
+      <c r="Q113" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P113" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q113" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R113" s="7"/>
@@ -20874,39 +20961,39 @@
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
       <c r="I114" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J114" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K114" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L114" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M114" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N114" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O114" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P114" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N114" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O114" s="57" t="str">
+      <c r="Q114" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P114" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q114" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R114" s="7"/>
@@ -20935,39 +21022,39 @@
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
       <c r="I115" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J115" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K115" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L115" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M115" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N115" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O115" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P115" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N115" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O115" s="57" t="str">
+      <c r="Q115" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P115" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q115" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R115" s="7"/>
@@ -20996,39 +21083,39 @@
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
       <c r="I116" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J116" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K116" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L116" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M116" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N116" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O116" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P116" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N116" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O116" s="57" t="str">
+      <c r="Q116" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P116" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q116" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R116" s="7"/>
@@ -21057,39 +21144,39 @@
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
       <c r="I117" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J117" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K117" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L117" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M117" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N117" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O117" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P117" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N117" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O117" s="57" t="str">
+      <c r="Q117" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P117" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q117" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R117" s="7"/>
@@ -21118,39 +21205,39 @@
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
       <c r="I118" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J118" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K118" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L118" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M118" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N118" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O118" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P118" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N118" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O118" s="57" t="str">
+      <c r="Q118" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P118" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q118" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R118" s="7"/>
@@ -21179,39 +21266,39 @@
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
       <c r="I119" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J119" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K119" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L119" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M119" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N119" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O119" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P119" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N119" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O119" s="57" t="str">
+      <c r="Q119" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P119" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q119" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R119" s="7"/>
@@ -21240,39 +21327,39 @@
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
       <c r="I120" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J120" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K120" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L120" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M120" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N120" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O120" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P120" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N120" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O120" s="57" t="str">
+      <c r="Q120" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P120" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q120" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R120" s="7"/>
@@ -21301,39 +21388,39 @@
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
       <c r="I121" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J121" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K121" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L121" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M121" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N121" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O121" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P121" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N121" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O121" s="57" t="str">
+      <c r="Q121" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P121" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q121" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R121" s="7"/>
@@ -21362,39 +21449,39 @@
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
       <c r="I122" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J122" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K122" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L122" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M122" s="56" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N122" s="56" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O122" s="57" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P122" s="57" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="N122" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O122" s="57" t="str">
+      <c r="Q122" s="57" t="str">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P122" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q122" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R122" s="7"/>
@@ -21423,39 +21510,39 @@
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
       <c r="I123" s="55" t="str">
-        <f t="shared" ref="I123:I127" si="37">IF(D123=0,"",LOG($K$15*10^D123+$K$16*10^E123+$K$14))</f>
+        <f t="shared" ref="I123:I127" si="39">IF(D123=0,"",LOG($K$15*10^D123+$K$16*10^E123+$K$14))</f>
         <v/>
       </c>
       <c r="J123" s="55" t="str">
-        <f t="shared" ref="J123:J127" si="38">IF(D123=0,"",LOG($K$21*10^D123+$K$22*10^E123+$K$20))</f>
+        <f t="shared" ref="J123:J127" si="40">IF(D123=0,"",LOG($K$21*10^D123+$K$22*10^E123+$K$20))</f>
         <v/>
       </c>
       <c r="K123" s="56" t="str">
-        <f t="shared" ref="K123:K127" si="39">IF(D123=0,"",1/(1+10^D123*$J$15/$J$14+10^E123*$J$16/$J$14+10^J123*$J$19/$J$14))</f>
+        <f t="shared" ref="K123:K127" si="41">IF(D123=0,"",1/(1+10^D123*$J$15/$J$14+10^E123*$J$16/$J$14+10^J123*$J$19/$J$14))</f>
         <v/>
       </c>
       <c r="L123" s="56" t="str">
-        <f t="shared" ref="L123:L127" si="40">IF(D123=0,"",1/(1+10^I123/10^J123*$J$13/$J$19))</f>
+        <f t="shared" ref="L123:L127" si="42">IF(D123=0,"",1/(1+10^I123/10^J123*$J$13/$J$19))</f>
         <v/>
       </c>
       <c r="M123" s="56" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N123" s="56" t="str">
-        <f t="shared" ref="N123:N127" si="41">IF(D123=0,"",1/(1/10^E123*$J$20/$J$22+10^D123/10^E123*$J$21/$J$22+10^I123/10^E123*$J$13/$J$22+1))</f>
+        <f t="shared" ref="N123:N127" si="43">IF(D123=0,"",1/(1/10^E123*$J$20/$J$22+10^D123/10^E123*$J$21/$J$22+10^I123/10^E123*$J$13/$J$22+1))</f>
         <v/>
       </c>
       <c r="O123" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="P123" s="57" t="str">
-        <f t="shared" ref="P123:P127" si="42">IF(D123=0,"",O123*10^J123)</f>
+        <f t="shared" ref="P123:P127" si="44">IF(D123=0,"",O123*10^J123)</f>
         <v/>
       </c>
       <c r="Q123" s="57" t="str">
-        <f t="shared" ref="Q123:Q127" si="43">IF(D123=0,"",F123*N123*$J$7/$J$22)</f>
+        <f t="shared" ref="Q123:Q127" si="45">IF(D123=0,"",F123*N123*$J$7/$J$22)</f>
         <v/>
       </c>
       <c r="R123" s="7"/>
@@ -21484,39 +21571,39 @@
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
       <c r="I124" s="55" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="J124" s="55" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="K124" s="56" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="L124" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M124" s="56" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="J124" s="55" t="str">
+      <c r="N124" s="56" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="O124" s="57" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="K124" s="56" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="L124" s="56" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M124" s="56" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N124" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="O124" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
       <c r="P124" s="57" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="Q124" s="57" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="R124" s="7"/>
@@ -21545,39 +21632,39 @@
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
       <c r="I125" s="55" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="J125" s="55" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="K125" s="56" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="L125" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M125" s="56" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="J125" s="55" t="str">
+      <c r="N125" s="56" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="O125" s="57" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="K125" s="56" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="L125" s="56" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M125" s="56" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N125" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="O125" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
       <c r="P125" s="57" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="Q125" s="57" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="R125" s="7"/>
@@ -21606,39 +21693,39 @@
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
       <c r="I126" s="55" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="J126" s="55" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="K126" s="56" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="L126" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M126" s="56" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="J126" s="55" t="str">
+      <c r="N126" s="56" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="O126" s="57" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="K126" s="56" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="L126" s="56" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M126" s="56" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N126" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="O126" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
       <c r="P126" s="57" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="Q126" s="57" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="R126" s="7"/>
@@ -21667,39 +21754,39 @@
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
       <c r="I127" s="55" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="J127" s="55" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="K127" s="56" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="L127" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M127" s="56" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="J127" s="55" t="str">
+      <c r="N127" s="56" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="O127" s="57" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="K127" s="56" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="L127" s="56" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M127" s="56" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N127" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="O127" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
       <c r="P127" s="57" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="Q127" s="57" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="R127" s="7"/>
@@ -25328,6 +25415,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="L8:Q8"/>
+    <mergeCell ref="L9:Q9"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="I24:Q25"/>
+    <mergeCell ref="I23:Q23"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L10:Q10"/>
+    <mergeCell ref="I11:Q11"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="L15:Q15"/>
+    <mergeCell ref="L16:Q16"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="G1:H77"/>
+    <mergeCell ref="L22:Q22"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="L6:Q6"/>
+    <mergeCell ref="L7:Q7"/>
+    <mergeCell ref="B24:F25"/>
+    <mergeCell ref="I17:Q17"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="L19:Q19"/>
+    <mergeCell ref="L20:Q20"/>
+    <mergeCell ref="L21:Q21"/>
     <mergeCell ref="I2:Q4"/>
     <mergeCell ref="I5:Q5"/>
     <mergeCell ref="B23:F23"/>
@@ -25344,46 +25467,181 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B8:F10"/>
     <mergeCell ref="B11:F12"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="L19:Q19"/>
-    <mergeCell ref="L20:Q20"/>
-    <mergeCell ref="L21:Q21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="L14:Q14"/>
-    <mergeCell ref="L15:Q15"/>
-    <mergeCell ref="L16:Q16"/>
-    <mergeCell ref="L18:Q18"/>
-    <mergeCell ref="G1:H77"/>
-    <mergeCell ref="L22:Q22"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="L6:Q6"/>
-    <mergeCell ref="L7:Q7"/>
-    <mergeCell ref="B24:F25"/>
-    <mergeCell ref="I17:Q17"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="I24:Q25"/>
-    <mergeCell ref="I23:Q23"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L10:Q10"/>
-    <mergeCell ref="I11:Q11"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FD1E138-77AF-40F1-A975-08CEAF6C12F1}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1">
+        <v>-0.73745450190951667</v>
+      </c>
+      <c r="B1">
+        <v>-1.5265197844064957</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>4.7386560000000006</v>
+      </c>
+      <c r="B2">
+        <v>5.8355820000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2.3724999877244022</v>
+      </c>
+      <c r="B3">
+        <v>2.8974999825375303</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>3.3511520000000004</v>
+      </c>
+      <c r="B4">
+        <v>4.2962190000000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>5.9183200000000005</v>
+      </c>
+      <c r="B5">
+        <v>7.0401399999999992</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>5.5295200000000007</v>
+      </c>
+      <c r="B6">
+        <v>6.5305900000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>5.4845040000000003</v>
+      </c>
+      <c r="B7">
+        <v>6.5678879999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>2.7195840000000011</v>
+      </c>
+      <c r="B8">
+        <v>3.2500779999999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>3.9841999877244016</v>
+      </c>
+      <c r="B9">
+        <v>5.1901999825375293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>4.10616</v>
+      </c>
+      <c r="B10">
+        <v>5.1108449999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>2.8295519999999996</v>
+      </c>
+      <c r="B11">
+        <v>3.5791989999999991</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>3.03</v>
+      </c>
+      <c r="B12">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>3.2352399999999997</v>
+      </c>
+      <c r="B13">
+        <v>3.7544849999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>3.3303280000000011</v>
+      </c>
+      <c r="B14">
+        <v>3.8215209999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>4.4202640000000004</v>
+      </c>
+      <c r="B15">
+        <v>5.6388380000000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>4.2752879999999998</v>
+      </c>
+      <c r="B16">
+        <v>5.3084609999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>2.7665919999999997</v>
+      </c>
+      <c r="B17">
+        <v>3.5255839999999989</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>4.4687359999999998</v>
+      </c>
+      <c r="B18">
+        <v>5.2666120000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>2.6972559999999999</v>
+      </c>
+      <c r="B19">
+        <v>3.431432</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>3.859360000000001</v>
+      </c>
+      <c r="B20">
+        <v>4.2614199999999993</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>